--- a/market-analysis/unit-economics-model.xlsx
+++ b/market-analysis/unit-economics-model.xlsx
@@ -23,8 +23,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="0.0%"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
   <fonts count="8">
@@ -87,12 +87,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
+        <fgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -127,7 +127,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,49 +140,50 @@
     <xf numFmtId="1" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -548,28 +549,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ПРИПУЩЕННЯ МОДЕЛІ — жовті комірки редагуються, решта рахується формулами</t>
+          <t>ПРИПУЩЕННЯ — жовті комірки редагуються, решта рахується формулами</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Змінюйте ЛИШЕ жовті комірки. Усі розрахунки на інших аркушах підтягнуться автоматично.</t>
+          <t>Редакція 2: ціни на послуги перевірено за публічними прайсами. Експорт вилучено з аналізу.</t>
         </is>
       </c>
     </row>
@@ -608,7 +609,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Курс USD/UAH (середній за рік)</t>
+          <t>Курс USD/UAH</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
@@ -625,14 +626,14 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>НБУ, серпень 2026: 44,5-45,0; прогноз кін.2026: 45,4-46,2</t>
+          <t>НБУ серпень 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Робочих днів на рік, польова бригада</t>
+          <t>Робочих днів, польова бригада</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
@@ -649,14 +650,14 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>250 календарних мінус відпустки/лікарняні</t>
+          <t>250 мінус відпустки/лікарняні</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Робочих днів на рік, бурова бригада</t>
+          <t>Робочих днів, бурова бригада</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
@@ -673,7 +674,7 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>нижче через сезонність і доступ на майданчики</t>
+          <t>сезонність, доступ на майданчики</t>
         </is>
       </c>
     </row>
@@ -697,14 +698,14 @@
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>1 780 доступних x 82% utilization</t>
+          <t>1 780 x 82% utilization</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>A. ТОПОГРАФО-ГЕОДЕЗИЧНА БРИГАДА (2 особи + авто + GNSS/тахеометр/дрон)</t>
+          <t>A. ГЕОДЕЗИЧНА БРИГАДА — ринкова ціна і ДВІ структури витрат</t>
         </is>
       </c>
     </row>
@@ -716,12 +717,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Значення</t>
+          <t>«Важка» структура</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>Од.</t>
+          <t>«Легка» структура</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr"/>
@@ -735,22 +736,20 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Денна ставка клієнту (середня по портфелю)</t>
+          <t>Денна ставка клієнту, грн</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>18000</v>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>грн/день</t>
-        </is>
+        <v>14000</v>
+      </c>
+      <c r="C12" s="8" t="n">
+        <v>14000</v>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
       <c r="E12" s="6" t="inlineStr"/>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>ринкова топозйомка М1:500 в перерахунку на бригадо-день</t>
+          <t>медіана перевірених прайсів (11-18 тис.)</t>
         </is>
       </c>
     </row>
@@ -763,18 +762,12 @@
       <c r="B13" s="9" t="n">
         <v>0.62</v>
       </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+      <c r="C13" s="9" t="n">
+        <v>0.62</v>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
       <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>погода, переїзди, простої, зимовий спад</t>
-        </is>
-      </c>
+      <c r="F13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -785,54 +778,44 @@
       <c r="B14" s="9" t="n">
         <v>0.75</v>
       </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
+      <c r="C14" s="9" t="n">
+        <v>0.75</v>
       </c>
       <c r="D14" s="6" t="inlineStr"/>
       <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>досяжно диспетчеризацією і мінімальним чеком</t>
-        </is>
-      </c>
+      <c r="F14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>ФОП бригади (інженер 52к + технік 30к), cost-to-company</t>
+          <t>ФОП бригади, грн/рік</t>
         </is>
       </c>
       <c r="B15" s="8" t="n">
         <v>984000</v>
       </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>грн/рік</t>
-        </is>
+      <c r="C15" s="8" t="n">
+        <v>840000</v>
       </c>
       <c r="D15" s="6" t="inlineStr"/>
       <c r="E15" s="6" t="inlineStr"/>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>82 000 грн/міс з податками</t>
+          <t>штат проти ФОП</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Камеральна обробка (0,4 FTE x 55 000)</t>
+          <t>Камеральна обробка, грн/рік</t>
         </is>
       </c>
       <c r="B16" s="8" t="n">
         <v>264000</v>
       </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>грн/рік</t>
-        </is>
+      <c r="C16" s="8" t="n">
+        <v>162000</v>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
       <c r="E16" s="6" t="inlineStr"/>
@@ -841,56 +824,54 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Авто: лізинг + ПММ + ТО</t>
+          <t>Авто, грн/рік</t>
         </is>
       </c>
       <c r="B17" s="8" t="n">
         <v>264000</v>
       </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>грн/рік</t>
-        </is>
+      <c r="C17" s="8" t="n">
+        <v>180000</v>
       </c>
       <c r="D17" s="6" t="inlineStr"/>
       <c r="E17" s="6" t="inlineStr"/>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>22 000 грн/міс</t>
+          <t>лізинг проти власного</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Амортизація приладів (GNSS+тахеометр+дрон ~$55к / 5 р.)</t>
+          <t>Амортизація приладів, грн/рік</t>
         </is>
       </c>
       <c r="B18" s="8" t="n">
         <v>495000</v>
       </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>грн/рік</t>
-        </is>
+      <c r="C18" s="8" t="n">
+        <v>270000</v>
       </c>
       <c r="D18" s="6" t="inlineStr"/>
       <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="6" t="inlineStr"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>нове $55к проти самортизованого</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>ПЗ, ліцензії, повірки, страхування</t>
+          <t>ПЗ, ліцензії, повірки, грн/рік</t>
         </is>
       </c>
       <c r="B19" s="8" t="n">
         <v>96000</v>
       </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>грн/рік</t>
-        </is>
+      <c r="C19" s="8" t="n">
+        <v>60000</v>
       </c>
       <c r="D19" s="6" t="inlineStr"/>
       <c r="E19" s="6" t="inlineStr"/>
@@ -899,16 +880,14 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Змінні витрати на польовий день (добові, житло, витратні)</t>
+          <t>Змінні на польовий день, грн</t>
         </is>
       </c>
       <c r="B20" s="8" t="n">
         <v>1400</v>
       </c>
-      <c r="C20" s="6" t="inlineStr">
-        <is>
-          <t>грн/день</t>
-        </is>
+      <c r="C20" s="8" t="n">
+        <v>1200</v>
       </c>
       <c r="D20" s="6" t="inlineStr"/>
       <c r="E20" s="6" t="inlineStr"/>
@@ -917,7 +896,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>B. ІНЖЕНЕРНО-ГЕОЛОГІЧНА (БУРОВА) БРИГАДА (3 особи + УРБ + лабораторія)</t>
+          <t>B. БУРОВА БРИГАДА — ТРИ структури витрат</t>
         </is>
       </c>
     </row>
@@ -929,15 +908,19 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Значення</t>
+          <t>Повна (нова УРБ)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>Од.</t>
-        </is>
-      </c>
-      <c r="D23" s="3" t="inlineStr"/>
+          <t>Самортизована УРБ</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>Мінімальна (2 особи)</t>
+        </is>
+      </c>
       <c r="E23" s="3" t="inlineStr"/>
       <c r="F23" s="3" t="inlineStr">
         <is>
@@ -948,226 +931,238 @@
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>Денна ставка (буріння + звіт)</t>
+          <t>Денна ставка клієнту, грн</t>
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>32000</v>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>грн/день</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="inlineStr"/>
+        <v>16000</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>16000</v>
+      </c>
+      <c r="D24" s="8" t="n">
+        <v>16000</v>
+      </c>
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>30-60 п.м./день, 600-900 грн/п.м.</t>
+          <t>медіана перевірених прайсів (13-20 тис.)</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>Utilization — поточний стан</t>
-        </is>
-      </c>
-      <c r="B25" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr"/>
+          <t>ФОП бригади, грн/рік</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>1488000</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>1488000</v>
+      </c>
+      <c r="D25" s="8" t="n">
+        <v>1104000</v>
+      </c>
       <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>3 особи проти 2</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Utilization — цільовий</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C26" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="inlineStr"/>
+          <t>Інженер-геолог + звіт, грн/рік</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n">
+        <v>504000</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>504000</v>
+      </c>
+      <c r="D26" s="8" t="n">
+        <v>504000</v>
+      </c>
       <c r="E26" s="6" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>ФОП бригади (бурмайстер 60к + 2 x 32к)</t>
+          <t>Амортизація/лізинг УРБ, грн/рік</t>
         </is>
       </c>
       <c r="B27" s="8" t="n">
-        <v>1488000</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>грн/рік</t>
-        </is>
-      </c>
-      <c r="D27" s="6" t="inlineStr"/>
+        <v>675000</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="8" t="n">
+        <v>0</v>
+      </c>
       <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>$90к / 6 років проти списаної</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Інженер-геолог + камеральний звіт (0,6 FTE x 70к)</t>
+          <t>Ремонт і ТО, грн/рік</t>
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>504000</v>
-      </c>
-      <c r="C28" s="6" t="inlineStr">
-        <is>
-          <t>грн/рік</t>
-        </is>
-      </c>
-      <c r="D28" s="6" t="inlineStr"/>
+        <v>240000</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>240000</v>
+      </c>
+      <c r="D28" s="8" t="n">
+        <v>240000</v>
+      </c>
       <c r="E28" s="6" t="inlineStr"/>
       <c r="F28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Амортизація/лізинг УРБ + інструмент (~$90к / 6 р.)</t>
+          <t>ПЗ, дозволи, ліцензії, грн/рік</t>
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>675000</v>
-      </c>
-      <c r="C29" s="6" t="inlineStr">
-        <is>
-          <t>грн/рік</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr"/>
+        <v>84000</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>84000</v>
+      </c>
+      <c r="D29" s="8" t="n">
+        <v>84000</v>
+      </c>
       <c r="E29" s="6" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Ремонт і ТО установки</t>
+          <t>Змінні на день, грн</t>
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>240000</v>
-      </c>
-      <c r="C30" s="6" t="inlineStr">
-        <is>
-          <t>грн/рік</t>
-        </is>
-      </c>
-      <c r="D30" s="6" t="inlineStr"/>
+        <v>5000</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D30" s="8" t="n">
+        <v>5000</v>
+      </c>
       <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>ПЗ, дозволи, ліцензії, страхування</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="n">
-        <v>84000</v>
-      </c>
-      <c r="C31" s="6" t="inlineStr">
-        <is>
-          <t>грн/рік</t>
-        </is>
-      </c>
-      <c r="D31" s="6" t="inlineStr"/>
+          <t>Лабораторія, % від виручки</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0.12</v>
+      </c>
       <c r="E31" s="6" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>Змінні на день (ПММ, обсадка, коронки, добові)</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C32" s="6" t="inlineStr">
-        <is>
-          <t>грн/день</t>
-        </is>
-      </c>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-    </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>Лабораторія (аутсорс), % від виручки</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C33" s="6" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>C. IT-ІНЖЕНЕР</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Стаття</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>Значення</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>Од.</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr"/>
+      <c r="E34" s="3" t="inlineStr"/>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>Коментар</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>C. IT-ІНЖЕНЕР (собівартість оплачуваної години)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Стаття</t>
-        </is>
-      </c>
-      <c r="B36" s="3" t="inlineStr">
-        <is>
-          <t>Значення</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Од.</t>
-        </is>
-      </c>
-      <c r="D36" s="3" t="inlineStr"/>
-      <c r="E36" s="3" t="inlineStr"/>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>Коментар</t>
-        </is>
-      </c>
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ЗП, cost-to-company</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="n">
+        <v>3100</v>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>$/міс</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr"/>
+      <c r="E35" s="6" t="inlineStr"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>ринок 2026: $1 000-5 500 за роллю</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>Податки, ЄСВ, адміністрування ФОП</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>% від ЗП</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr"/>
+      <c r="E36" s="6" t="inlineStr"/>
+      <c r="F36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>ЗП, cost-to-company (mix middle/senior)</t>
+          <t>Робоче місце, обладнання, ПЗ</t>
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>3100</v>
+        <v>450</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
@@ -1176,20 +1171,16 @@
       </c>
       <c r="D37" s="6" t="inlineStr"/>
       <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>DOU/ринок 2026</t>
-        </is>
-      </c>
+      <c r="F37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Податки, ЄСВ, адміністрування ФОП</t>
+          <t>Розподіл non-billable ролей</t>
         </is>
       </c>
       <c r="B38" s="9" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
@@ -1200,160 +1191,124 @@
       <c r="E38" s="6" t="inlineStr"/>
       <c r="F38" s="6" t="inlineStr"/>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>Робоче місце, обладнання, ПЗ, навчання</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="n">
-        <v>450</v>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
-        <is>
-          <t>$/міс</t>
-        </is>
-      </c>
-      <c r="D39" s="6" t="inlineStr"/>
-      <c r="E39" s="6" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr"/>
-    </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>Розподіл non-billable ролей (тімлід/PM/QA-менеджмент)</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>% від ЗП</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr"/>
-      <c r="E40" s="6" t="inlineStr"/>
-      <c r="F40" s="6" t="inlineStr"/>
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>D. ПІДПИСКИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>ARPA $/рік</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>CAC $</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>Річний churn</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>Коментар</t>
+        </is>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>D. ПІДПИСКОВІ МОДЕЛІ</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Модель</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>ARPA $/рік</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="D43" s="3" t="inlineStr">
-        <is>
-          <t>CAC $</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>Річний churn</t>
-        </is>
-      </c>
-      <c r="F43" s="3" t="inlineStr">
-        <is>
-          <t>Коментар</t>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>D1 SaaS — мережі й інфраструктурні активи</t>
+        </is>
+      </c>
+      <c r="B42" s="8" t="n">
+        <v>14000</v>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="D42" s="8" t="n">
+        <v>8500</v>
+      </c>
+      <c r="E42" s="9" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>увага: CloudCity уже у водоканалах</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>D2 DaaS-моніторинг обʼєкта</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n">
+        <v>6670</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="D43" s="8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E43" s="9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>продається наявним клієнтам геодезії</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>D1 Вертикальний SaaS — мережі й інфраструктурні активи</t>
+          <t>D3 Агро-продукт</t>
         </is>
       </c>
       <c r="B44" s="8" t="n">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="C44" s="9" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="D44" s="8" t="n">
-        <v>8500</v>
+        <v>16000</v>
       </c>
       <c r="E44" s="9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>ентерпрайз-цикл 5-8 міс</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>D2 DaaS-моніторинг обʼєкта (дрон + фотограмметрія + дашборд)</t>
-        </is>
-      </c>
-      <c r="B45" s="8" t="n">
-        <v>6670</v>
-      </c>
-      <c r="C45" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="D45" s="8" t="n">
-        <v>1800</v>
-      </c>
-      <c r="E45" s="9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>продається наявним клієнтам геодезії → CAC мінімальний</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>D3 Агро-продукт (для порівняння)</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="n">
-        <v>9000</v>
-      </c>
-      <c r="C46" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="D46" s="8" t="n">
-        <v>16000</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>Cropio/Syngenta, OneSoil, Soft.Farm — ринок зайнятий</t>
+          <t>Cropio, OneSoil, Soft.Farm — ринок зайнятий</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A35:H35"/>
     <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A33:H33"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A22:H22"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1365,700 +1320,631 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="44" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ЮНІТ-ЕКОНОМІКА ЗА НАПРЯМКАМИ — усе рахується з аркуша «1.Припущення»</t>
+          <t>ЮНІТ-ЕКОНОМІКА — усе рахується з аркуша «1.Припущення»</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>A. ТОПОГРАФО-ГЕОДЕЗИЧНА БРИГАДА — прибуток на 1 бригаду на рік</t>
+          <t>A. ГЕОДЕЗІЯ: та сама ринкова ціна, дві структури витрат</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Сценарій</t>
+          <t>Показник</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Оплач. днів</t>
+          <t>«Важка»</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Виручка, грн</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Витрати, грн</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Валовий приб.</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>GM %</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>ВП на 1 FTE, $</t>
-        </is>
-      </c>
+          <t>«Легка»</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr"/>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" s="3" t="inlineStr"/>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>Поточний стан: util 62%, 18 000 грн/день</t>
+          <t>Фіксовані витрати, грн/рік</t>
         </is>
       </c>
       <c r="B5" s="10">
-        <f>'1.Припущення'!B6*'1.Припущення'!B13</f>
-        <v/>
-      </c>
-      <c r="C5" s="11">
-        <f>B5*'1.Припущення'!B12</f>
-        <v/>
-      </c>
-      <c r="D5" s="11">
-        <f>('1.Припущення'!B15+'1.Припущення'!B16+'1.Припущення'!B17+'1.Припущення'!B18+'1.Припущення'!B19)+B5*'1.Припущення'!B20</f>
-        <v/>
-      </c>
-      <c r="E5" s="11">
-        <f>C5-D5</f>
-        <v/>
-      </c>
-      <c r="F5" s="12">
-        <f>E5/C5</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
-        <f>E5/2.4/'1.Припущення'!B5</f>
+        <f>('1.Припущення'!B15+'1.Припущення'!B16+'1.Припущення'!B17+'1.Припущення'!B18+'1.Припущення'!B19)</f>
+        <v/>
+      </c>
+      <c r="C5" s="10">
+        <f>('1.Припущення'!C15+'1.Припущення'!C16+'1.Припущення'!C17+'1.Припущення'!C18+'1.Припущення'!C19)</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Ціль-1: util 75%, ставка без змін</t>
-        </is>
-      </c>
-      <c r="B6" s="13">
-        <f>'1.Припущення'!B6*'1.Припущення'!B14</f>
-        <v/>
-      </c>
-      <c r="C6" s="14">
-        <f>B6*'1.Припущення'!B12</f>
-        <v/>
-      </c>
-      <c r="D6" s="14">
-        <f>('1.Припущення'!B15+'1.Припущення'!B16+'1.Припущення'!B17+'1.Припущення'!B18+'1.Припущення'!B19)+B6*'1.Припущення'!B20</f>
-        <v/>
-      </c>
-      <c r="E6" s="14">
-        <f>C6-D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="15">
-        <f>E6/C6</f>
-        <v/>
-      </c>
-      <c r="G6" s="14">
-        <f>E6/2.4/'1.Припущення'!B5</f>
+          <t>Точка беззбитковості, днів</t>
+        </is>
+      </c>
+      <c r="B6" s="11">
+        <f>('1.Припущення'!B15+'1.Припущення'!B16+'1.Припущення'!B17+'1.Припущення'!B18+'1.Припущення'!B19)/('1.Припущення'!B12-'1.Припущення'!B20)</f>
+        <v/>
+      </c>
+      <c r="C6" s="11">
+        <f>('1.Припущення'!C15+'1.Припущення'!C16+'1.Припущення'!C17+'1.Припущення'!C18+'1.Припущення'!C19)/('1.Припущення'!B12-'1.Припущення'!C20)</f>
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Ціль-2: util 75% + ставка 22 000 (+20%)</t>
-        </is>
-      </c>
-      <c r="B7" s="13">
-        <f>'1.Припущення'!B6*'1.Припущення'!B14</f>
-        <v/>
-      </c>
-      <c r="C7" s="14">
-        <f>B7*22000</f>
-        <v/>
-      </c>
-      <c r="D7" s="14">
-        <f>('1.Припущення'!B15+'1.Припущення'!B16+'1.Припущення'!B17+'1.Припущення'!B18+'1.Припущення'!B19)+B7*'1.Припущення'!B20</f>
-        <v/>
-      </c>
-      <c r="E7" s="14">
-        <f>C7-D7</f>
-        <v/>
-      </c>
-      <c r="F7" s="15">
-        <f>E7/C7</f>
-        <v/>
-      </c>
-      <c r="G7" s="14">
-        <f>E7/2.4/'1.Припущення'!B5</f>
+          <t>Точка беззбитковості, % utilization</t>
+        </is>
+      </c>
+      <c r="B7" s="12">
+        <f>B6/'1.Припущення'!B6</f>
+        <v/>
+      </c>
+      <c r="C7" s="12">
+        <f>C6/'1.Припущення'!B6</f>
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Стрес: util 50%, ставка 16 000</t>
-        </is>
-      </c>
-      <c r="B8" s="16">
-        <f>'1.Припущення'!B6*0.5</f>
-        <v/>
-      </c>
-      <c r="C8" s="17">
-        <f>B8*16000</f>
-        <v/>
-      </c>
-      <c r="D8" s="17">
-        <f>('1.Припущення'!B15+'1.Припущення'!B16+'1.Припущення'!B17+'1.Припущення'!B18+'1.Припущення'!B19)+B8*'1.Припущення'!B20</f>
-        <v/>
-      </c>
-      <c r="E8" s="17">
-        <f>C8-D8</f>
-        <v/>
-      </c>
-      <c r="F8" s="18">
-        <f>E8/C8</f>
-        <v/>
-      </c>
-      <c r="G8" s="17">
-        <f>E8/2.4/'1.Припущення'!B5</f>
+          <t>@62%: виручка</t>
+        </is>
+      </c>
+      <c r="B8" s="10">
+        <f>'1.Припущення'!B6*'1.Припущення'!B13*'1.Припущення'!B12</f>
+        <v/>
+      </c>
+      <c r="C8" s="10">
+        <f>'1.Припущення'!B6*'1.Припущення'!B13*'1.Припущення'!B12</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="19" t="inlineStr">
-        <is>
-          <t>Точка беззбитковості, днів →</t>
-        </is>
-      </c>
-      <c r="B9" s="20">
-        <f>('1.Припущення'!B15+'1.Припущення'!B16+'1.Припущення'!B17+'1.Припущення'!B18+'1.Припущення'!B19)/('1.Припущення'!B12-'1.Припущення'!B20)</f>
-        <v/>
-      </c>
-      <c r="C9" s="21">
-        <f>B9/'1.Припущення'!B6</f>
-        <v/>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>utilization — нижче цього бригада збиткова</t>
-        </is>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>@62%: витрати</t>
+        </is>
+      </c>
+      <c r="B9" s="10">
+        <f>('1.Припущення'!B15+'1.Припущення'!B16+'1.Припущення'!B17+'1.Припущення'!B18+'1.Припущення'!B19)+'1.Припущення'!B6*'1.Припущення'!B13*'1.Припущення'!B20</f>
+        <v/>
+      </c>
+      <c r="C9" s="10">
+        <f>('1.Припущення'!C15+'1.Припущення'!C16+'1.Припущення'!C17+'1.Припущення'!C18+'1.Припущення'!C19)+'1.Припущення'!B6*'1.Припущення'!B13*'1.Припущення'!C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>@62%: ВАЛОВИЙ ПРИБУТОК</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>B8-B9</f>
+        <v/>
+      </c>
+      <c r="C10" s="15">
+        <f>C8-C9</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>B. БУРОВА БРИГАДА — прибуток на 1 установку на рік</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Сценарій</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Оплач. днів</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Виручка, грн</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>Витрати, грн</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>Валовий приб.</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>GM %</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>ВП на 1 FTE, $</t>
-        </is>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>@62%: GM</t>
+        </is>
+      </c>
+      <c r="B11" s="16">
+        <f>B10/B8</f>
+        <v/>
+      </c>
+      <c r="C11" s="17">
+        <f>C10/C8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>@75%: виручка</t>
+        </is>
+      </c>
+      <c r="B12" s="10">
+        <f>'1.Припущення'!B6*'1.Припущення'!B14*'1.Припущення'!B12</f>
+        <v/>
+      </c>
+      <c r="C12" s="10">
+        <f>'1.Припущення'!B6*'1.Припущення'!B14*'1.Припущення'!B12</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Поточний стан: util 55%, 32 000 грн/день</t>
-        </is>
-      </c>
-      <c r="B13" s="16">
-        <f>'1.Припущення'!B7*'1.Припущення'!B25</f>
-        <v/>
-      </c>
-      <c r="C13" s="17">
-        <f>B13*'1.Припущення'!B24</f>
-        <v/>
-      </c>
-      <c r="D13" s="17">
-        <f>('1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29+'1.Припущення'!B30+'1.Припущення'!B31)+B13*'1.Припущення'!B32+C13*'1.Припущення'!B33</f>
-        <v/>
-      </c>
-      <c r="E13" s="17">
-        <f>C13-D13</f>
-        <v/>
-      </c>
-      <c r="F13" s="18">
-        <f>E13/C13</f>
-        <v/>
-      </c>
-      <c r="G13" s="17">
-        <f>E13/3.6/'1.Припущення'!B5</f>
+          <t>@75%: витрати</t>
+        </is>
+      </c>
+      <c r="B13" s="10">
+        <f>('1.Припущення'!B15+'1.Припущення'!B16+'1.Припущення'!B17+'1.Припущення'!B18+'1.Припущення'!B19)+'1.Припущення'!B6*'1.Припущення'!B14*'1.Припущення'!B20</f>
+        <v/>
+      </c>
+      <c r="C13" s="10">
+        <f>('1.Припущення'!C15+'1.Припущення'!C16+'1.Припущення'!C17+'1.Припущення'!C18+'1.Припущення'!C19)+'1.Припущення'!B6*'1.Припущення'!B14*'1.Припущення'!C20</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>Ціль-1: util 70%, ставка без змін</t>
-        </is>
-      </c>
-      <c r="B14" s="10">
-        <f>'1.Припущення'!B7*'1.Припущення'!B26</f>
-        <v/>
-      </c>
-      <c r="C14" s="11">
-        <f>B14*'1.Припущення'!B24</f>
-        <v/>
-      </c>
-      <c r="D14" s="11">
-        <f>('1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29+'1.Припущення'!B30+'1.Припущення'!B31)+B14*'1.Припущення'!B32+C14*'1.Припущення'!B33</f>
-        <v/>
-      </c>
-      <c r="E14" s="11">
-        <f>C14-D14</f>
-        <v/>
-      </c>
-      <c r="F14" s="12">
-        <f>E14/C14</f>
-        <v/>
-      </c>
-      <c r="G14" s="11">
-        <f>E14/3.6/'1.Припущення'!B5</f>
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>@75%: ВАЛОВИЙ ПРИБУТОК</t>
+        </is>
+      </c>
+      <c r="B14" s="14">
+        <f>B12-B13</f>
+        <v/>
+      </c>
+      <c r="C14" s="15">
+        <f>C12-C13</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Ціль-2: util 70% + ставка 38 000 (+19%)</t>
-        </is>
-      </c>
-      <c r="B15" s="13">
-        <f>'1.Припущення'!B7*'1.Припущення'!B26</f>
-        <v/>
-      </c>
-      <c r="C15" s="14">
-        <f>B15*38000</f>
-        <v/>
-      </c>
-      <c r="D15" s="14">
-        <f>('1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29+'1.Припущення'!B30+'1.Припущення'!B31)+B15*'1.Припущення'!B32+C15*'1.Припущення'!B33</f>
-        <v/>
-      </c>
-      <c r="E15" s="14">
-        <f>C15-D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="15">
-        <f>E15/C15</f>
-        <v/>
-      </c>
-      <c r="G15" s="14">
-        <f>E15/3.6/'1.Припущення'!B5</f>
+          <t>@75%: GM</t>
+        </is>
+      </c>
+      <c r="B15" s="16">
+        <f>B14/B12</f>
+        <v/>
+      </c>
+      <c r="C15" s="17">
+        <f>C14/C12</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>Стрес: util 45%, ставка 30 000</t>
-        </is>
-      </c>
-      <c r="B16" s="16">
-        <f>'1.Припущення'!B7*0.45</f>
-        <v/>
-      </c>
-      <c r="C16" s="17">
-        <f>B16*30000</f>
-        <v/>
-      </c>
-      <c r="D16" s="17">
-        <f>('1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29+'1.Припущення'!B30+'1.Припущення'!B31)+B16*'1.Припущення'!B32+C16*'1.Припущення'!B33</f>
-        <v/>
-      </c>
-      <c r="E16" s="17">
-        <f>C16-D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="18">
-        <f>E16/C16</f>
-        <v/>
-      </c>
-      <c r="G16" s="17">
-        <f>E16/3.6/'1.Припущення'!B5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="19" t="inlineStr">
-        <is>
-          <t>Точка беззбитковості, днів →</t>
-        </is>
-      </c>
-      <c r="B17" s="20">
-        <f>('1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29+'1.Припущення'!B30+'1.Припущення'!B31)/('1.Припущення'!B24-'1.Припущення'!B32-'1.Припущення'!B24*'1.Припущення'!B33)</f>
-        <v/>
-      </c>
-      <c r="C17" s="21">
-        <f>B17/'1.Припущення'!B7</f>
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>Різниця «легка» − «важка» при 62% завантаження, грн/рік</t>
+        </is>
+      </c>
+      <c r="B16" s="19">
+        <f>C10-B10</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>C. IT-ІНЖЕНЕР — собівартість години і маржа за ринками збуту</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="inlineStr">
+          <t>B. ГЕОЛОГІЯ: за якої ставки бригада виходить у нуль?</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Ставка, грн/бригадо-день</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Внесок на день</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Повна (нова УРБ)</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>Самортизована УРБ</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>Мінімальна (2 особи)</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>13000</v>
+      </c>
+      <c r="B21" s="10">
+        <f>A21-'1.Припущення'!B30-A21*'1.Припущення'!B31</f>
+        <v/>
+      </c>
+      <c r="C21" s="20">
+        <f>('1.Припущення'!B25+'1.Припущення'!B26+'1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29)/$B$21</f>
+        <v/>
+      </c>
+      <c r="D21" s="20">
+        <f>('1.Припущення'!C25+'1.Припущення'!C26+'1.Припущення'!C27+'1.Припущення'!C28+'1.Припущення'!C29)/$B$21</f>
+        <v/>
+      </c>
+      <c r="E21" s="20">
+        <f>('1.Припущення'!D25+'1.Припущення'!D26+'1.Припущення'!D27+'1.Припущення'!D28+'1.Припущення'!D29)/$B$21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n">
+        <v>16000</v>
+      </c>
+      <c r="B22" s="10">
+        <f>A22-'1.Припущення'!B30-A22*'1.Припущення'!B31</f>
+        <v/>
+      </c>
+      <c r="C22" s="20">
+        <f>('1.Припущення'!B25+'1.Припущення'!B26+'1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29)/$B$22</f>
+        <v/>
+      </c>
+      <c r="D22" s="20">
+        <f>('1.Припущення'!C25+'1.Припущення'!C26+'1.Припущення'!C27+'1.Припущення'!C28+'1.Припущення'!C29)/$B$22</f>
+        <v/>
+      </c>
+      <c r="E22" s="20">
+        <f>('1.Припущення'!D25+'1.Припущення'!D26+'1.Припущення'!D27+'1.Припущення'!D28+'1.Припущення'!D29)/$B$22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>20000</v>
+      </c>
+      <c r="B23" s="10">
+        <f>A23-'1.Припущення'!B30-A23*'1.Припущення'!B31</f>
+        <v/>
+      </c>
+      <c r="C23" s="20">
+        <f>('1.Припущення'!B25+'1.Припущення'!B26+'1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29)/$B$23</f>
+        <v/>
+      </c>
+      <c r="D23" s="20">
+        <f>('1.Припущення'!C25+'1.Припущення'!C26+'1.Припущення'!C27+'1.Припущення'!C28+'1.Припущення'!C29)/$B$23</f>
+        <v/>
+      </c>
+      <c r="E23" s="20">
+        <f>('1.Припущення'!D25+'1.Припущення'!D26+'1.Припущення'!D27+'1.Припущення'!D28+'1.Припущення'!D29)/$B$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>29000</v>
+      </c>
+      <c r="B24" s="10">
+        <f>A24-'1.Припущення'!B30-A24*'1.Припущення'!B31</f>
+        <v/>
+      </c>
+      <c r="C24" s="20">
+        <f>('1.Припущення'!B25+'1.Припущення'!B26+'1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29)/$B$24</f>
+        <v/>
+      </c>
+      <c r="D24" s="20">
+        <f>('1.Припущення'!C25+'1.Припущення'!C26+'1.Припущення'!C27+'1.Припущення'!C28+'1.Припущення'!C29)/$B$24</f>
+        <v/>
+      </c>
+      <c r="E24" s="20">
+        <f>('1.Припущення'!D25+'1.Припущення'!D26+'1.Припущення'!D27+'1.Припущення'!D28+'1.Припущення'!D29)/$B$24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>Доступних робочих днів на рік →</t>
+        </is>
+      </c>
+      <c r="B25" s="21">
+        <f>'1.Припущення'!B7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Читати так: якщо число днів БІЛЬШЕ за 210 — беззбитковість недосяжна за жодного завантаження.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Ринок платить 13-20 тис. Для нуля при 70% завантаження потрібно ~29 тис. Розрив 1,8x.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>C. IT-ІНЖЕНЕР — собівартість оплачуваної години</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Повна вартість інженера, $/рік</t>
         </is>
       </c>
-      <c r="B20" s="22">
-        <f>'1.Припущення'!B37*12*(1+'1.Припущення'!B38+'1.Припущення'!B40)+'1.Припущення'!B39*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="B31" s="23">
+        <f>'1.Припущення'!B35*12*(1+'1.Припущення'!B36+'1.Припущення'!B38)+'1.Припущення'!B37*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>Собівартість 1 оплачуваної години, $</t>
         </is>
       </c>
-      <c r="B21" s="23">
-        <f>$B$20/'1.Припущення'!B8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>Ринок збуту</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B32" s="24">
+        <f>$B$31/'1.Припущення'!B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Ринок збуту (тільки внутрішній)</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>Ставка $/год</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>ВП $/год</t>
         </is>
       </c>
-      <c r="D22" s="3" t="inlineStr">
-        <is>
-          <t>GM %</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
         <is>
           <t>ВП на інженера $/рік</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr"/>
-      <c r="G22" s="3" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>Внутрішній UA, T&amp;M (будівельники / агро / дороги)</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
+      <c r="F33" s="3" t="inlineStr"/>
+      <c r="G33" s="3" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>Внутрішній UA, T&amp;M, сеньйорна команда</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="n">
         <v>26</v>
       </c>
-      <c r="C23" s="24">
-        <f>B23-$B$21</f>
-        <v/>
-      </c>
-      <c r="D23" s="25">
-        <f>C23/B23</f>
-        <v/>
-      </c>
-      <c r="E23" s="17">
-        <f>C23*'1.Припущення'!B8</f>
-        <v/>
-      </c>
-      <c r="F23" s="26" t="inlineStr">
+      <c r="C34" s="25">
+        <f>B34-$B$32</f>
+        <v/>
+      </c>
+      <c r="D34" s="16">
+        <f>C34/B34</f>
+        <v/>
+      </c>
+      <c r="E34" s="26">
+        <f>C34*'1.Припущення'!B8</f>
+        <v/>
+      </c>
+      <c r="F34" s="27" t="inlineStr">
         <is>
           <t>збиткова модель</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Внутрішній UA, держ- і донорські проєкти</t>
         </is>
       </c>
-      <c r="B24" s="7" t="n">
+      <c r="B35" s="7" t="n">
         <v>38</v>
       </c>
-      <c r="C24" s="24">
-        <f>B24-$B$21</f>
-        <v/>
-      </c>
-      <c r="D24" s="25">
-        <f>C24/B24</f>
-        <v/>
-      </c>
-      <c r="E24" s="17">
-        <f>C24*'1.Припущення'!B8</f>
-        <v/>
-      </c>
-      <c r="F24" s="26" t="inlineStr">
+      <c r="C35" s="25">
+        <f>B35-$B$32</f>
+        <v/>
+      </c>
+      <c r="D35" s="16">
+        <f>C35/B35</f>
+        <v/>
+      </c>
+      <c r="E35" s="26">
+        <f>C35*'1.Припущення'!B8</f>
+        <v/>
+      </c>
+      <c r="F35" s="27" t="inlineStr">
         <is>
           <t>на межі нуля</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>Експорт EU, geospatial-ніша</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n">
-        <v>55</v>
-      </c>
-      <c r="C25" s="27">
-        <f>B25-$B$21</f>
-        <v/>
-      </c>
-      <c r="D25" s="28">
-        <f>C25/B25</f>
-        <v/>
-      </c>
-      <c r="E25" s="14">
-        <f>C25*'1.Припущення'!B8</f>
-        <v/>
-      </c>
-      <c r="F25" s="29" t="inlineStr">
-        <is>
-          <t>робоча модель</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>Експорт US/UK, geospatial-ніша</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="n">
-        <v>68</v>
-      </c>
-      <c r="C26" s="27">
-        <f>B26-$B$21</f>
-        <v/>
-      </c>
-      <c r="D26" s="28">
-        <f>C26/B26</f>
-        <v/>
-      </c>
-      <c r="E26" s="14">
-        <f>C26*'1.Припущення'!B8</f>
-        <v/>
-      </c>
-      <c r="F26" s="29" t="inlineStr">
-        <is>
-          <t>ціль</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>D. ПІДПИСКОВІ МОДЕЛІ — LTV, CAC, payback</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Експортні ставки вилучено з моделі на вимогу власника.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>D. ПІДПИСКИ — єдина модель, що дає маржу на внутрішньому ринку</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="30" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
         <is>
           <t>Модель</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B39" s="3" t="inlineStr">
         <is>
           <t>LTV $</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
+      <c r="C39" s="3" t="inlineStr">
         <is>
           <t>LTV / CAC</t>
         </is>
       </c>
-      <c r="D29" s="3" t="inlineStr">
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>CAC payback, міс</t>
         </is>
       </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>Клієнтів до беззбитковості*</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>Клієнтів до беззбитковості</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
         <is>
           <t>Вердикт</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>D1 Вертикальний SaaS — мережі й інфраструктура</t>
-        </is>
-      </c>
-      <c r="B30" s="14">
+      <c r="G39" s="3" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>D1 SaaS — мережі й інфраструктура</t>
+        </is>
+      </c>
+      <c r="B40" s="28">
+        <f>'1.Припущення'!B42*'1.Припущення'!C42/'1.Припущення'!E42</f>
+        <v/>
+      </c>
+      <c r="C40" s="29">
+        <f>B40/'1.Припущення'!D42</f>
+        <v/>
+      </c>
+      <c r="D40" s="29">
+        <f>'1.Припущення'!D42/('1.Припущення'!B42*'1.Припущення'!C42/12)</f>
+        <v/>
+      </c>
+      <c r="E40" s="30">
+        <f>(8*$B$31+60000)/('1.Припущення'!B42*'1.Припущення'!C42)</f>
+        <v/>
+      </c>
+      <c r="F40" s="31" t="inlineStr">
+        <is>
+          <t>ІНВЕСТУВАТИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>D2 DaaS-моніторинг обʼєкта</t>
+        </is>
+      </c>
+      <c r="B41" s="28">
+        <f>'1.Припущення'!B43*'1.Припущення'!C43/'1.Припущення'!E43</f>
+        <v/>
+      </c>
+      <c r="C41" s="29">
+        <f>B41/'1.Припущення'!D43</f>
+        <v/>
+      </c>
+      <c r="D41" s="29">
+        <f>'1.Припущення'!D43/('1.Припущення'!B43*'1.Припущення'!C43/12)</f>
+        <v/>
+      </c>
+      <c r="E41" s="30">
+        <f>(3*$B$31+20000)/('1.Припущення'!B43*'1.Припущення'!C43)</f>
+        <v/>
+      </c>
+      <c r="F41" s="31" t="inlineStr">
+        <is>
+          <t>ІНВЕСТУВАТИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>D3 Агро-продукт</t>
+        </is>
+      </c>
+      <c r="B42" s="26">
         <f>'1.Припущення'!B44*'1.Припущення'!C44/'1.Припущення'!E44</f>
         <v/>
       </c>
-      <c r="C30" s="27">
-        <f>B30/'1.Припущення'!D44</f>
-        <v/>
-      </c>
-      <c r="D30" s="27">
+      <c r="C42" s="25">
+        <f>B42/'1.Припущення'!D44</f>
+        <v/>
+      </c>
+      <c r="D42" s="25">
         <f>'1.Припущення'!D44/('1.Припущення'!B44*'1.Припущення'!C44/12)</f>
         <v/>
       </c>
-      <c r="E30" s="13">
-        <f>(8*$B$20+60000)/('1.Припущення'!B44*'1.Припущення'!C44)</f>
-        <v/>
-      </c>
-      <c r="F30" s="29" t="inlineStr">
-        <is>
-          <t>ІНВЕСТУВАТИ</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>D2 DaaS-моніторинг обʼєкта</t>
-        </is>
-      </c>
-      <c r="B31" s="14">
-        <f>'1.Припущення'!B45*'1.Припущення'!C45/'1.Припущення'!E45</f>
-        <v/>
-      </c>
-      <c r="C31" s="27">
-        <f>B31/'1.Припущення'!D45</f>
-        <v/>
-      </c>
-      <c r="D31" s="27">
-        <f>'1.Припущення'!D45/('1.Припущення'!B45*'1.Припущення'!C45/12)</f>
-        <v/>
-      </c>
-      <c r="E31" s="13">
-        <f>(3*$B$20+20000)/('1.Припущення'!B45*'1.Припущення'!C45)</f>
-        <v/>
-      </c>
-      <c r="F31" s="29" t="inlineStr">
-        <is>
-          <t>ІНВЕСТУВАТИ — найшвидший payback</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>D3 Агро-продукт</t>
-        </is>
-      </c>
-      <c r="B32" s="17">
-        <f>'1.Припущення'!B46*'1.Припущення'!C46/'1.Припущення'!E46</f>
-        <v/>
-      </c>
-      <c r="C32" s="24">
-        <f>B32/'1.Припущення'!D46</f>
-        <v/>
-      </c>
-      <c r="D32" s="24">
-        <f>'1.Припущення'!D46/('1.Припущення'!B46*'1.Припущення'!C46/12)</f>
-        <v/>
-      </c>
-      <c r="E32" s="16">
-        <f>(8*$B$20+60000)/('1.Припущення'!B46*'1.Припущення'!C46)</f>
-        <v/>
-      </c>
-      <c r="F32" s="26" t="inlineStr">
-        <is>
-          <t>НЕ ІНВЕСТУВАТИ</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>* при команді D1/D3 = 8 FTE, D2 = 3 FTE. Орієнтир здорової моделі: LTV/CAC &gt; 3, payback &lt; 12 міс.</t>
+      <c r="E42" s="20">
+        <f>(8*$B$31+60000)/('1.Припущення'!B44*'1.Припущення'!C44)</f>
+        <v/>
+      </c>
+      <c r="F42" s="27" t="inlineStr">
+        <is>
+          <t>НІ — payback 30 міс</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Орієнтир здорової моделі: LTV/CAC &gt; 3, payback &lt; 12 міс.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2070,34 +1956,34 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="8" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ОБСЯГИ РИНКІВ І ПОТЕНЦІАЛ КОМПАНІЇ, млн грн</t>
+          <t>ВНУТРІШНІЙ РИНОК: TAM / SAM / SOM 2026-2029, млн грн (експорт вилучено)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TAM — увесь ринок · SAM — доступний нам сегмент · SOM — реалістична виручка GIS-Point · FTE — скільки людей треба, щоб цей SOM узяти</t>
+          <t>FTE — скільки людей потрібно, щоб узяти цей SOM у 2029. Темпи знижено після даних Держстату за січень-квітень 2026 (−2% р/р).</t>
         </is>
       </c>
     </row>
@@ -2159,488 +2045,445 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Головний драйвер / гальмо</t>
+          <t>Драйвер / гальмо</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>M1  Топогеодезичні вишукування (UA)</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="n">
-        <v>2860</v>
-      </c>
-      <c r="C5" s="11" t="n">
-        <v>3318</v>
-      </c>
-      <c r="D5" s="11" t="n">
-        <v>3882</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>4464</v>
-      </c>
-      <c r="F5" s="11" t="n">
-        <v>1518</v>
-      </c>
-      <c r="G5" s="11" t="n">
-        <v>34</v>
-      </c>
-      <c r="H5" s="11" t="n">
-        <v>91</v>
-      </c>
-      <c r="I5" s="30" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="J5" s="11">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>M6  Мережі й комунальна інфраструктура</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="n">
+        <v>950</v>
+      </c>
+      <c r="C5" s="28" t="n">
+        <v>1159</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <v>1437</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>614</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>80</v>
+      </c>
+      <c r="I5" s="17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J5" s="28">
         <f>H5*I5</f>
         <v/>
       </c>
-      <c r="K5" s="10" t="n">
-        <v>35</v>
+      <c r="K5" s="30" t="n">
+        <v>23</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>БМР 258→292 млрд грн; вишукування ~0,55% від БМР</t>
+          <t>RDNA5: енергетика в топ-3 збитків; донори вимагають облік активів</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
-        <is>
-          <t>M2  Інженерно-геологічні вишукування (UA)</t>
-        </is>
-      </c>
-      <c r="B6" s="17" t="n">
-        <v>2410</v>
-      </c>
-      <c r="C6" s="17" t="n">
-        <v>2772</v>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>3215</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>3665</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G6" s="17" t="n">
-        <v>22</v>
-      </c>
-      <c r="H6" s="17" t="n">
-        <v>49</v>
-      </c>
-      <c r="I6" s="25" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="J6" s="17">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>M5  Дорожники та інфраструктура</t>
+        </is>
+      </c>
+      <c r="B6" s="28" t="n">
+        <v>650</v>
+      </c>
+      <c r="C6" s="28" t="n">
+        <v>767</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>959</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>1189</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>357</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>46</v>
+      </c>
+      <c r="I6" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J6" s="28">
         <f>H6*I6</f>
         <v/>
       </c>
-      <c r="K6" s="16" t="n">
-        <v>15</v>
+      <c r="K6" s="30" t="n">
+        <v>14</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>той самий драйвер, але капіталомісткість убиває маржу</t>
+          <t>дорфонд 12,6 млрд при потребі 52 млрд; донори</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>M3  ІТ-автоматизація для будівельників (UA)</t>
-        </is>
-      </c>
-      <c r="B7" s="11" t="n">
-        <v>990</v>
-      </c>
-      <c r="C7" s="11" t="n">
-        <v>1267</v>
-      </c>
-      <c r="D7" s="11" t="n">
-        <v>1647</v>
-      </c>
-      <c r="E7" s="11" t="n">
-        <v>2109</v>
-      </c>
-      <c r="F7" s="11" t="n">
+          <t>M1  Топографо-геодезичні вишукування</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>2860</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>3089</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>3367</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>3636</v>
+      </c>
+      <c r="F7" s="10" t="n">
+        <v>1236</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="H7" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="I7" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J7" s="10">
+        <f>H7*I7</f>
+        <v/>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>базовий обсяг; зростання лише інфляційне</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>M9  Надра й карʼєри: маркшейдерія + DaaS</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="n">
         <v>380</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="C8" s="28" t="n">
+        <v>426</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>481</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>534</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>240</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J8" s="28">
+        <f>H8*I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="H7" s="11" t="n">
-        <v>34</v>
-      </c>
-      <c r="I7" s="30" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="J7" s="11">
-        <f>H7*I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>9</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>BIM на держзамовленні, ЄДЕССБ; але SAM лише 380 млн</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="26" t="inlineStr">
-        <is>
-          <t>M4  ІТ/цифра для агро (UA)</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="n">
-        <v>3890</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <v>4551</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <v>5280</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <v>6071</v>
-      </c>
-      <c r="F8" s="17" t="n">
-        <v>486</v>
-      </c>
-      <c r="G8" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="H8" s="17" t="n">
-        <v>29</v>
-      </c>
-      <c r="I8" s="25" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J8" s="17">
-        <f>H8*I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>8</v>
-      </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>24 млн га x $3,6/га; ринок зайнятий, CAC високий</t>
+          <t>обовʼязкові заміри, майже немає конкуренції</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>M5  ІТ/геодані для дорожників та інфри (UA)</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="n">
-        <v>650</v>
-      </c>
-      <c r="C9" s="11" t="n">
-        <v>812</v>
-      </c>
-      <c r="D9" s="11" t="n">
-        <v>1072</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <v>1394</v>
-      </c>
-      <c r="F9" s="11" t="n">
-        <v>418</v>
-      </c>
-      <c r="G9" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="H9" s="11" t="n">
-        <v>46</v>
-      </c>
-      <c r="I9" s="30" t="n">
+          <t>M3  ІТ-автоматизація для будівельників</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>990</v>
+      </c>
+      <c r="C9" s="10" t="n">
+        <v>1208</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1510</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F9" s="10" t="n">
+        <v>337</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="H9" s="10" t="n">
+        <v>34</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J9" s="10">
+        <f>H9*I9</f>
+        <v/>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>BIM на держзамовленні, ЄДЕССБ; SAM лише 337 млн</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>M8  Розмінування: геодані + ІТ</t>
+        </is>
+      </c>
+      <c r="B10" s="10" t="n">
+        <v>260</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>299</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <v>353</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>406</v>
+      </c>
+      <c r="F10" s="10" t="n">
+        <v>162</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I10" s="12" t="n">
         <v>0.55</v>
       </c>
-      <c r="J9" s="11">
-        <f>H9*I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>14</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>дорфонд 12,6 млрд при потребі 52 млрд; донори</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>M6  Мережі й комунальна інфраструктура (UA)</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n">
-        <v>950</v>
-      </c>
-      <c r="C10" s="14" t="n">
-        <v>1197</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>1532</v>
-      </c>
-      <c r="E10" s="14" t="n">
-        <v>1915</v>
-      </c>
-      <c r="F10" s="14" t="n">
-        <v>670</v>
-      </c>
-      <c r="G10" s="14" t="n">
+      <c r="J10" s="10">
+        <f>H10*I10</f>
+        <v/>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>GIS = ядро IMSMA; фінансування політичне</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>M4  ІТ / цифра для агро</t>
+        </is>
+      </c>
+      <c r="B11" s="26" t="n">
+        <v>3890</v>
+      </c>
+      <c r="C11" s="26" t="n">
+        <v>4435</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>5055</v>
+      </c>
+      <c r="E11" s="26" t="n">
+        <v>5713</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>457</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H11" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="I11" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J11" s="26">
+        <f>H11*I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>найбільший TAM — і LTV/CAC 1,8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>M2  Інженерно-геологічні вишукування</t>
+        </is>
+      </c>
+      <c r="B12" s="26" t="n">
+        <v>2410</v>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>2579</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>2785</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>2980</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>894</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="I12" s="16" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J12" s="26">
+        <f>H12*I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="H10" s="14" t="n">
-        <v>80</v>
-      </c>
-      <c r="I10" s="28" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="J10" s="14">
-        <f>H10*I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="13" t="n">
-        <v>24</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>RDNA5: енергетика в топ-3 збитків; донори вимагають облік активів</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="26" t="inlineStr">
-        <is>
-          <t>M7  Громади / містобудівна документація (UA)</t>
-        </is>
-      </c>
-      <c r="B11" s="17" t="n">
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>беззбитковість недосяжна за ринковою ціною</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>M7  Громади / містобудівна документація</t>
+        </is>
+      </c>
+      <c r="B13" s="26" t="n">
         <v>750</v>
       </c>
-      <c r="C11" s="17" t="n">
-        <v>862</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>1141</v>
-      </c>
-      <c r="F11" s="17" t="n">
-        <v>285</v>
-      </c>
-      <c r="G11" s="17" t="n">
+      <c r="C13" s="26" t="n">
+        <v>825</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>916</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>1007</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <v>252</v>
+      </c>
+      <c r="G13" s="26" t="n">
         <v>4</v>
       </c>
-      <c r="H11" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="I11" s="25" t="n">
+      <c r="H13" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="I13" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="J11" s="17">
-        <f>H11*I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>обовʼязкові комплексні плани; але тендери й демпінг</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>M8  Розмінування: геодані + ІТ (UA)</t>
-        </is>
-      </c>
-      <c r="B12" s="11" t="n">
-        <v>260</v>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>312</v>
-      </c>
-      <c r="D12" s="11" t="n">
-        <v>381</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>449</v>
-      </c>
-      <c r="F12" s="11" t="n">
-        <v>180</v>
-      </c>
-      <c r="G12" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="H12" s="11" t="n">
-        <v>13</v>
-      </c>
-      <c r="I12" s="30" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J12" s="11">
-        <f>H12*I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>2,5 млрд грн ринку; фінансування політично волатильне</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>M9  Надра/карʼєри: маркшейдерія + DaaS (UA)</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>380</v>
-      </c>
-      <c r="C13" s="14" t="n">
-        <v>433</v>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>498</v>
-      </c>
-      <c r="E13" s="14" t="n">
-        <v>563</v>
-      </c>
-      <c r="F13" s="14" t="n">
-        <v>253</v>
-      </c>
-      <c r="G13" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>15</v>
-      </c>
-      <c r="I13" s="28" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="J13" s="14">
+      <c r="J13" s="26">
         <f>H13*I13</f>
         <v/>
       </c>
-      <c r="K13" s="13" t="n">
-        <v>5</v>
+      <c r="K13" s="20" t="n">
+        <v>3</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>~1 500 надрокористувачів, обовʼязкові обсяги; ринок малий</t>
+          <t>тендери, демпінг, дрібні чеки</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>M10 ЕКСПОРТ geospatial (доступний сегмент)</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>14400</v>
-      </c>
-      <c r="C14" s="14" t="n">
-        <v>16128</v>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>18063</v>
-      </c>
-      <c r="E14" s="14" t="n">
-        <v>20231</v>
-      </c>
-      <c r="F14" s="14" t="n">
-        <v>20231</v>
-      </c>
-      <c r="G14" s="14" t="n">
-        <v>36</v>
-      </c>
-      <c r="H14" s="14" t="n">
-        <v>223</v>
-      </c>
-      <c r="I14" s="28" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J14" s="14">
-        <f>H14*I14</f>
-        <v/>
-      </c>
-      <c r="K14" s="13" t="n">
-        <v>54</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>глобальний ринок ~$103 млрд, CAGR 11-12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="31" t="inlineStr">
+      <c r="A14" s="32" t="inlineStr">
         <is>
           <t>РАЗОМ</t>
         </is>
       </c>
-      <c r="B15" s="32">
-        <f>SUM(B5:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="32">
-        <f>SUM(C5:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="32">
-        <f>SUM(D5:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="32">
-        <f>SUM(E5:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="32">
-        <f>SUM(F5:F14)</f>
-        <v/>
-      </c>
-      <c r="G15" s="32">
-        <f>SUM(G5:G14)</f>
-        <v/>
-      </c>
-      <c r="H15" s="32">
-        <f>SUM(H5:H14)</f>
-        <v/>
-      </c>
-      <c r="I15" s="31" t="n"/>
-      <c r="J15" s="32">
-        <f>SUM(J5:J14)</f>
-        <v/>
-      </c>
-      <c r="K15" s="33">
-        <f>SUM(K5:K14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="34" t="inlineStr">
-        <is>
-          <t>ГОЛОВНЕ ОБМЕЖЕННЯ: щоб узяти весь SOM, потрібно ~171 людину. Компанія планує 100. Отже, ВИБІР ОБОВʼЯЗКОВИЙ — можна взяти приблизно 60% списку.</t>
+      <c r="B14" s="33">
+        <f>SUM(B5:B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="33">
+        <f>SUM(C5:C13)</f>
+        <v/>
+      </c>
+      <c r="D14" s="33">
+        <f>SUM(D5:D13)</f>
+        <v/>
+      </c>
+      <c r="E14" s="33">
+        <f>SUM(E5:E13)</f>
+        <v/>
+      </c>
+      <c r="F14" s="33">
+        <f>SUM(F5:F13)</f>
+        <v/>
+      </c>
+      <c r="G14" s="33">
+        <f>SUM(G5:G13)</f>
+        <v/>
+      </c>
+      <c r="H14" s="33">
+        <f>SUM(H5:H13)</f>
+        <v/>
+      </c>
+      <c r="I14" s="32" t="n"/>
+      <c r="J14" s="33">
+        <f>SUM(J5:J13)</f>
+        <v/>
+      </c>
+      <c r="K14" s="34">
+        <f>SUM(K5:K13)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Увесь внутрішній SOM потребує ~115 людей при плані 100. Без експорту кожна відмова прямо зменшує виручку — компенсувати нічим.</t>
         </is>
       </c>
     </row>
@@ -2658,31 +2501,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="44" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>МАТРИЦЯ РІШЕННЯ — чому ранжування за ВП/FTE оманливе</t>
+          <t>МАТРИЦЯ РІШЕННЯ — чому ранжування за одним показником оманливе</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Оцінка 1-5 за пʼятьма критеріями. Ваги — у рядку 4, їх можна змінювати (жовті).</t>
+          <t>Оцінка 1-5. Ваги в рядку 5 редагуються.</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2577,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>ВАГА</t>
         </is>
@@ -2756,133 +2599,133 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="31" t="inlineStr">
         <is>
           <t>M6  Мережі й комунальна інфра</t>
         </is>
       </c>
-      <c r="B6" s="13" t="n">
+      <c r="B6" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="30" t="n">
         <v>3</v>
       </c>
       <c r="G6" s="35">
         <f>SUMPRODUCT(B6:F6,$B$5:$F$5)</f>
         <v/>
       </c>
-      <c r="H6" s="29" t="inlineStr">
+      <c r="H6" s="31" t="inlineStr">
         <is>
           <t>★★★ ЯДРО</t>
         </is>
       </c>
-      <c r="I6" s="29" t="inlineStr">
-        <is>
-          <t>LTV/CAC 10,7; ми єдині, хто і знімає дані в полі, і будує систему</t>
+      <c r="I6" s="31" t="inlineStr">
+        <is>
+          <t>єдиний рядок, де великий ВП/FTE поєднується з масштабом</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>M10 ЕКСПОРТ geospatial</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="13" t="n">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>M5  Дорожники та інфраструктура</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="E7" s="30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F7" s="30" t="n">
         <v>2</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>5</v>
       </c>
       <c r="G7" s="35">
         <f>SUMPRODUCT(B7:F7,$B$5:$F$5)</f>
         <v/>
       </c>
-      <c r="H7" s="29" t="inlineStr">
-        <is>
-          <t>★★★ ЯДРО</t>
-        </is>
-      </c>
-      <c r="I7" s="29" t="inlineStr">
-        <is>
-          <t>єдина лінія, прибуткова у ВСІХ трьох сценаріях; вхід у продажі дорогий</t>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>★★ ДВИГУН</t>
+        </is>
+      </c>
+      <c r="I7" s="31" t="inlineStr">
+        <is>
+          <t>донорські гроші й вимога прозорості; ризик держзамовника</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="31" t="inlineStr">
         <is>
           <t>M9  Надра/карʼєри: DaaS-обʼєми</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C8" s="13" t="n">
+      <c r="B8" s="30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="30" t="n">
         <v>4</v>
       </c>
       <c r="G8" s="35">
         <f>SUMPRODUCT(B8:F8,$B$5:$F$5)</f>
         <v/>
       </c>
-      <c r="H8" s="29" t="inlineStr">
-        <is>
-          <t>★★★ ЯДРО (мала ставка)</t>
-        </is>
-      </c>
-      <c r="I8" s="29" t="inlineStr">
-        <is>
-          <t>LTV/CAC 13,3, payback 4,5 міс — але ринок малий, це не двигун</t>
+      <c r="H8" s="31" t="inlineStr">
+        <is>
+          <t>★★ ДВИГУН</t>
+        </is>
+      </c>
+      <c r="I8" s="31" t="inlineStr">
+        <is>
+          <t>LTV/CAC 13,3; та сама технологія, що й M5 — одна команда</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>M5  ІТ/геодані для дорожників</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
+          <t>M1  Топогеодезичні вишукування</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C9" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="D9" s="10" t="n">
+      <c r="C9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <v>3</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>2</v>
       </c>
       <c r="G9" s="36">
         <f>SUMPRODUCT(B9:F9,$B$5:$F$5)</f>
@@ -2890,35 +2733,35 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>★★ ОПЦІЯ</t>
+          <t>● КЕШ + КАНАЛ</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>донорські гроші й вимога прозорості — наш продаж; ризик держзамовника</t>
+          <t>33 людини заради 23 млн ВП, але робить CAC підписки $1 800</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>M1  Топогеодезичні вишукування</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
+          <t>M3  ІТ для будівельників</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="F10" s="10" t="n">
+      <c r="D10" s="11" t="n">
         <v>3</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>2</v>
       </c>
       <c r="G10" s="36">
         <f>SUMPRODUCT(B10:F10,$B$5:$F$5)</f>
@@ -2926,12 +2769,12 @@
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>● КЕШ + КАНАЛ</t>
+          <t>◐ опція</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>не двигун росту, але дає гроші й майже нульовий CAC для підписок</t>
+          <t>SAM лише 337 млн грн</t>
         </is>
       </c>
     </row>
@@ -2941,19 +2784,19 @@
           <t>M8  Розмінування: геодані + ІТ</t>
         </is>
       </c>
-      <c r="B11" s="10" t="n">
+      <c r="B11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="C11" s="10" t="n">
+      <c r="C11" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="E11" s="10" t="n">
+      <c r="E11" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="11" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="36">
@@ -2962,154 +2805,118 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>◐ спостерігати</t>
+          <t>◐ опція</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>унікальний фіт (GIS = ядро IMSMA), але фінансування політичне</t>
+          <t>унікальний фіт, але фінансування політичне</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="26" t="inlineStr">
-        <is>
-          <t>M3  ІТ для будівельників (UA)</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="n">
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>M4  ІТ / цифра для агро</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="16" t="n">
+      <c r="C12" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="20" t="n">
         <v>2</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>4</v>
       </c>
       <c r="G12" s="37">
         <f>SUMPRODUCT(B12:F12,$B$5:$F$5)</f>
         <v/>
       </c>
-      <c r="H12" s="26" t="inlineStr">
+      <c r="H12" s="27" t="inlineStr">
         <is>
           <t>✗ НІ</t>
         </is>
       </c>
-      <c r="I12" s="26" t="inlineStr">
-        <is>
-          <t>SAM лише 380 млн грн; галузь платить мало і повільно</t>
+      <c r="I12" s="27" t="inlineStr">
+        <is>
+          <t>LTV/CAC 1,8, payback 30,5 міс — ринок зайнятий</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="26" t="inlineStr">
-        <is>
-          <t>M4  ІТ/цифра для агро (UA)</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="n">
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>M2  Інженерно-геологічні вишукування</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="20" t="n">
         <v>2</v>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>4</v>
       </c>
       <c r="G13" s="37">
         <f>SUMPRODUCT(B13:F13,$B$5:$F$5)</f>
         <v/>
       </c>
-      <c r="H13" s="26" t="inlineStr">
-        <is>
-          <t>✗ НІ</t>
-        </is>
-      </c>
-      <c r="I13" s="26" t="inlineStr">
-        <is>
-          <t>LTV/CAC 1,8, payback 30 міс — Cropio, OneSoil, Soft.Farm вже там</t>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>✗ ЗМІНИТИ РОЛЬ</t>
+        </is>
+      </c>
+      <c r="I13" s="27" t="inlineStr">
+        <is>
+          <t>беззбитковість недосяжна: треба 29 тис./день, ринок дає 16 тис.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="26" t="inlineStr">
-        <is>
-          <t>M2  Інженерно-геологічні вишукування</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="n">
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>M7  Громади / містобудівна докум.</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="16" t="n">
+      <c r="C14" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="20" t="n">
         <v>2</v>
       </c>
       <c r="G14" s="37">
         <f>SUMPRODUCT(B14:F14,$B$5:$F$5)</f>
         <v/>
       </c>
-      <c r="H14" s="26" t="inlineStr">
-        <is>
-          <t>✗ ЗГОРНУТИ</t>
-        </is>
-      </c>
-      <c r="I14" s="26" t="inlineStr">
-        <is>
-          <t>GM 12%, беззбитковість 61% util — найгірша економіка портфеля</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="inlineStr">
-        <is>
-          <t>M7  Громади / містобудівна докум.</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="C15" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="G15" s="37">
-        <f>SUMPRODUCT(B15:F15,$B$5:$F$5)</f>
-        <v/>
-      </c>
-      <c r="H15" s="26" t="inlineStr">
+      <c r="H14" s="27" t="inlineStr">
         <is>
           <t>✗ НІ</t>
         </is>
       </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="I14" s="27" t="inlineStr">
         <is>
           <t>тендери, демпінг, дрібні чеки</t>
         </is>
@@ -3132,33 +2939,33 @@
   <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>P&amp;L: БАЗА 2026 → ЦІЛЬ 2029</t>
+          <t>P&amp;L: БАЗА 2026 → ЦІЛЬ 2029 (тільки внутрішній ринок)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="38" t="inlineStr">
         <is>
-          <t>База 2026 — реконструкція за ринково-типовими ставками, НЕ фактична звітність компанії. Замініть на свої цифри.</t>
+          <t>База 2026 — реконструкція за РИНКОВИМИ цінами і «легкою» структурою витрат, НЕ ваша звітність.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>БАЗА 2026 (~50 осіб) — поточний портфель</t>
+          <t>БАЗА 2026 (~50 осіб) — перерахована за ринковими цінами</t>
         </is>
       </c>
     </row>
@@ -3205,26 +3012,26 @@
           <t>Топогеодезія</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="11" t="n">
         <v>22</v>
       </c>
       <c r="C6" s="39" t="n">
         <v>62</v>
       </c>
-      <c r="D6" s="30" t="n">
-        <v>0.18</v>
+      <c r="D6" s="12" t="n">
+        <v>0.19</v>
       </c>
       <c r="E6" s="39">
         <f>C6*D6</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="10">
         <f>IF(B6=0,0,E6*1000000/45.0/B6)</f>
         <v/>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>util ~62%, ставка ~18 000 грн/день</t>
+          <t>util ~62%, ставка 14 000 грн/день, «легка» структура</t>
         </is>
       </c>
     </row>
@@ -3234,26 +3041,26 @@
           <t>Геологія (буріння)</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C7" s="39" t="n">
-        <v>34</v>
-      </c>
-      <c r="D7" s="30" t="n">
-        <v>0.06</v>
+        <v>30</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>0.03</v>
       </c>
       <c r="E7" s="39">
         <f>C7*D7</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="10">
         <f>IF(B7=0,0,E7*1000000/45.0/B7)</f>
         <v/>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>util ~55% — нижче точки беззбитковості</t>
+          <t>нижче точки беззбитковості за ринковою ціною</t>
         </is>
       </c>
     </row>
@@ -3263,26 +3070,26 @@
           <t>ІТ на внутрішній ринок</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="11" t="n">
         <v>10</v>
       </c>
       <c r="C8" s="39" t="n">
         <v>17</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="12" t="n">
         <v>0.12</v>
       </c>
       <c r="E8" s="39">
         <f>C8*D8</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="10">
         <f>IF(B8=0,0,E8*1000000/45.0/B8)</f>
         <v/>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>фікс-прайс проєкти; T&amp;M за $26/год був би збитковим</t>
+          <t>фікс-прайс; T&amp;M за $26/год був би збитковим</t>
         </is>
       </c>
     </row>
@@ -3292,32 +3099,32 @@
           <t>Адмін / продажі / бек-офіс</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C9" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="39">
         <f>C9*D9</f>
         <v/>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="10">
         <f>IF(B9=0,0,E9*1000000/45.0/B9)</f>
         <v/>
       </c>
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="31" t="inlineStr">
+      <c r="A10" s="32" t="inlineStr">
         <is>
           <t>РАЗОМ</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="32">
         <f>SUM(B6:B9)</f>
         <v/>
       </c>
@@ -3333,14 +3140,14 @@
         <f>SUM(E6:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="32">
+      <c r="F10" s="33">
         <f>E10*1000000/45.0/B10</f>
         <v/>
       </c>
-      <c r="G10" s="31" t="inlineStr"/>
+      <c r="G10" s="32" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>SG&amp;A, % від виручки</t>
         </is>
@@ -3359,7 +3166,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="31" t="inlineStr">
+      <c r="A12" s="32" t="inlineStr">
         <is>
           <t>EBITDA, млн грн</t>
         </is>
@@ -3386,7 +3193,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ЦІЛЬ 2029 (~100 осіб) — рекомендований портфель</t>
+          <t>ЦІЛЬ 2029 (~100 осіб) — тільки внутрішній ринок</t>
         </is>
       </c>
     </row>
@@ -3430,58 +3237,58 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Експорт geospatial IT</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>32</v>
+          <t>Мережі / комунальна інфра: продукт + підписка</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="n">
+        <v>20</v>
       </c>
       <c r="C16" s="39" t="n">
-        <v>108</v>
-      </c>
-      <c r="D16" s="30" t="n">
-        <v>0.38</v>
+        <v>65</v>
+      </c>
+      <c r="D16" s="12" t="n">
+        <v>0.62</v>
       </c>
       <c r="E16" s="39">
         <f>C16*D16</f>
         <v/>
       </c>
-      <c r="F16" s="11">
+      <c r="F16" s="10">
         <f>IF(B16=0,0,E16*1000000/51.5/B16)</f>
         <v/>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>26 billable інженерів x $55/год</t>
+          <t>~90 ентерпрайз-акаунтів</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Мережі / інфра: продукт + підписка</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>20</v>
+          <t>Топогеодезія (кеш + канал продажів)</t>
+        </is>
+      </c>
+      <c r="B17" s="11" t="n">
+        <v>33</v>
       </c>
       <c r="C17" s="39" t="n">
-        <v>68</v>
-      </c>
-      <c r="D17" s="30" t="n">
-        <v>0.62</v>
+        <v>87</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>0.26</v>
       </c>
       <c r="E17" s="39">
         <f>C17*D17</f>
         <v/>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="10">
         <f>IF(B17=0,0,E17*1000000/51.5/B17)</f>
         <v/>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>~95 ентерпрайз-акаунтів</t>
+          <t>«легка» структура + util 75% + чек 50 тис.</t>
         </is>
       </c>
     </row>
@@ -3491,20 +3298,20 @@
           <t>Дороги / інфра: геодані і контроль</t>
         </is>
       </c>
-      <c r="B18" s="10" t="n">
-        <v>12</v>
+      <c r="B18" s="11" t="n">
+        <v>14</v>
       </c>
       <c r="C18" s="39" t="n">
-        <v>40</v>
-      </c>
-      <c r="D18" s="30" t="n">
+        <v>46</v>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>0.52</v>
       </c>
       <c r="E18" s="39">
         <f>C18*D18</f>
         <v/>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="10">
         <f>IF(B18=0,0,E18*1000000/51.5/B18)</f>
         <v/>
       </c>
@@ -3517,122 +3324,122 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>DaaS-моніторинг (надра, будмайданчики)</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>8</v>
+          <t>Надра / карʼєри: DaaS-заміри обсягів</t>
+        </is>
+      </c>
+      <c r="B19" s="11" t="n">
+        <v>7</v>
       </c>
       <c r="C19" s="39" t="n">
-        <v>30</v>
-      </c>
-      <c r="D19" s="30" t="n">
-        <v>0.68</v>
+        <v>21</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <v>0.66</v>
       </c>
       <c r="E19" s="39">
         <f>C19*D19</f>
         <v/>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="10">
         <f>IF(B19=0,0,E19*1000000/51.5/B19)</f>
         <v/>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>~80 обʼєктів під підпискою</t>
+          <t>та сама технологія, що й дороги</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Топогеодезія (виконання + канал продажів)</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>20</v>
+          <t>ІТ для будівельників (BIM / ЄДЕССБ)</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>8</v>
       </c>
       <c r="C20" s="39" t="n">
-        <v>78</v>
-      </c>
-      <c r="D20" s="30" t="n">
-        <v>0.28</v>
+        <v>28</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>0.45</v>
       </c>
       <c r="E20" s="39">
         <f>C20*D20</f>
         <v/>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="10">
         <f>IF(B20=0,0,E20*1000000/51.5/B20)</f>
         <v/>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>util 75% + ставка +20%; НЕ росте у людях</t>
+          <t>продукт, не години</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Геологія (партнерська модель)</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n">
+          <t>Розмінування: геодані + звітність</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n">
         <v>4</v>
       </c>
       <c r="C21" s="39" t="n">
-        <v>20</v>
-      </c>
-      <c r="D21" s="30" t="n">
-        <v>0.14</v>
+        <v>13</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>0.55</v>
       </c>
       <c r="E21" s="39">
         <f>C21*D21</f>
         <v/>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="10">
         <f>IF(B21=0,0,E21*1000000/51.5/B21)</f>
         <v/>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>власні установки продані/здані, роботи через партнерів</t>
+          <t>опція, не ставка</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Адмін / продажі / маркетинг / R&amp;D-платформа</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="n">
-        <v>4</v>
+          <t>Адмін / продажі / маркетинг / R&amp;D</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>14</v>
       </c>
       <c r="C22" s="39" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="30" t="n">
+      <c r="D22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E22" s="39">
         <f>C22*D22</f>
         <v/>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="10">
         <f>IF(B22=0,0,E22*1000000/51.5/B22)</f>
         <v/>
       </c>
       <c r="G22" s="4" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="inlineStr">
+      <c r="A23" s="32" t="inlineStr">
         <is>
           <t>РАЗОМ</t>
         </is>
       </c>
-      <c r="B23" s="31">
+      <c r="B23" s="32">
         <f>SUM(B16:B22)</f>
         <v/>
       </c>
@@ -3648,20 +3455,20 @@
         <f>SUM(E16:E22)</f>
         <v/>
       </c>
-      <c r="F23" s="32">
+      <c r="F23" s="33">
         <f>E23*1000000/51.5/B23</f>
         <v/>
       </c>
-      <c r="G23" s="31" t="inlineStr"/>
+      <c r="G23" s="32" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="19" t="inlineStr">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>SG&amp;A, % від виручки</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="C24" s="42">
         <f>C23*B24</f>
@@ -3674,7 +3481,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="inlineStr">
+      <c r="A25" s="32" t="inlineStr">
         <is>
           <t>EBITDA, млн грн</t>
         </is>
@@ -3774,177 +3581,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="44" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="44" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>СЦЕНАРІЇ 2029</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
+          <t>СЦЕНАРІЇ 2029 — ціна відмови від валютної виручки</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="38" t="inlineStr">
+        <is>
+          <t>Без експорту всі шість напрямків живляться з одного джерела: бюджету й донорських грошей.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Сценарій</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Ймовірність</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Коеф. внутр. ринків</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Коеф. експорту</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Виручка, млн грн</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>EBITDA, млн грн</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Що це означає</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>A. Війна триває, донори стабільні</t>
-        </is>
-      </c>
-      <c r="B4" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C4" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" s="11">
-        <f>(68+40+30+78+20)*C4+108*D4</f>
-        <v/>
-      </c>
-      <c r="F4" s="11">
-        <f>(68*0.62+40*0.52+30*0.68+78*0.28+20*0.14)*C4+108*0.38*D4-E4*0.26</f>
-        <v/>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>базовий портфель без змін</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>B. Перемирʼя + донорський пакет</t>
+          <t>A. Війна триває, донори стабільні</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>0.25</v>
+        <v>0.55</v>
       </c>
       <c r="C5" s="50" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="D5" s="50" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E5" s="11">
-        <f>(68+40+30+78+20)*C5+108*D5</f>
-        <v/>
-      </c>
-      <c r="F5" s="11">
-        <f>(68*0.62+40*0.52+30*0.68+78*0.28+20*0.14)*C5+108*0.38*D5-E5*0.26</f>
-        <v/>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>інфра, мережі й дороги стрибають; експорт росте помірно</t>
+        <v>1</v>
+      </c>
+      <c r="D5" s="10">
+        <f>(65+87+46+21+28+13)*C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="10">
+        <f>(65*0.62+87*0.26+46*0.52+21*0.66+28*0.45+13*0.55)*C5-D5*0.27</f>
+        <v/>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>базовий портфель</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>B. Перемирʼя + донорський пакет</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="50" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="D6" s="10">
+        <f>(65+87+46+21+28+13)*C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="10">
+        <f>(65*0.62+87*0.26+46*0.52+21*0.66+28*0.45+13*0.55)*C6-D6*0.27</f>
+        <v/>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>інфра, мережі й дороги стрибають</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="27" t="inlineStr">
+        <is>
           <t>C. Ескалація / зрив фінансування</t>
         </is>
       </c>
-      <c r="B6" s="9" t="n">
+      <c r="B7" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="C6" s="50" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D6" s="50" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="E6" s="11">
-        <f>(68+40+30+78+20)*C6+108*D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="11">
-        <f>(68*0.62+40*0.52+30*0.68+78*0.28+20*0.14)*C6+108*0.38*D6-E6*0.26</f>
-        <v/>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>внутрішні ринки -45%; експорт майже не страждає</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="31" t="inlineStr">
+      <c r="C7" s="51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D7" s="26">
+        <f>(65+87+46+21+28+13)*C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="26">
+        <f>(65*0.62+87*0.26+46*0.52+21*0.66+28*0.45+13*0.55)*C7-D7*0.27</f>
+        <v/>
+      </c>
+      <c r="F7" s="27" t="inlineStr">
+        <is>
+          <t>виручка падає удвічі — нижню межу не тримає ніщо</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="32" t="inlineStr">
         <is>
           <t>ОЧІКУВАНЕ ЗНАЧЕННЯ (зважене)</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n"/>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="31" t="n"/>
-      <c r="E7" s="32">
-        <f>SUMPRODUCT(B4:B6,E4:E6)</f>
-        <v/>
-      </c>
-      <c r="F7" s="32">
-        <f>SUMPRODUCT(B4:B6,F4:F6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="34" t="inlineStr">
-        <is>
-          <t>ВИСНОВОК: експорт — єдина лінія, що дає прибуток у всіх трьох сценаріях. Це не «додатковий напрямок», а страховка всієї компанії.</t>
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="33">
+        <f>SUMPRODUCT(B5:B7,D5:D7)</f>
+        <v/>
+      </c>
+      <c r="E8" s="33">
+        <f>SUMPRODUCT(B5:B7,E5:E7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>Раніше експорт тримав нижню межу: внутрішні ринки падали на 45%, валютна лінія майже ні. Тепер такої лінії немає.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/market-analysis/unit-economics-model.xlsx
+++ b/market-analysis/unit-economics-model.xlsx
@@ -23,11 +23,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,6 +52,10 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
     </font>
     <font>
       <b val="1"/>
@@ -127,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,38 +154,40 @@
     <xf numFmtId="9" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="9" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -570,7 +576,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Редакція 2: ціни на послуги перевірено за публічними прайсами. Експорт вилучено з аналізу.</t>
+          <t>Редакція 3: денні ставки — ФАКТИЧНІ дані власника. Експорт вилучено з аналізу.</t>
         </is>
       </c>
     </row>
@@ -740,16 +746,16 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
       <c r="E12" s="6" t="inlineStr"/>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>медіана перевірених прайсів (11-18 тис.)</t>
+          <t>ФАКТ власника, разом із камеральною обробкою</t>
         </is>
       </c>
     </row>
@@ -935,18 +941,18 @@
         </is>
       </c>
       <c r="B24" s="8" t="n">
-        <v>16000</v>
+        <v>70000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>16000</v>
+        <v>70000</v>
       </c>
       <c r="D24" s="8" t="n">
-        <v>16000</v>
+        <v>70000</v>
       </c>
       <c r="E24" s="6" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>медіана перевірених прайсів (13-20 тис.)</t>
+          <t>ФАКТ власника: буріння + лабораторія + звіт</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -1581,7 +1587,7 @@
     </row>
     <row r="21">
       <c r="A21" s="8" t="n">
-        <v>13000</v>
+        <v>40000</v>
       </c>
       <c r="B21" s="10">
         <f>A21-'1.Припущення'!B30-A21*'1.Припущення'!B31</f>
@@ -1601,8 +1607,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
-        <v>16000</v>
+      <c r="A22" s="8" t="n">
+        <v>55000</v>
       </c>
       <c r="B22" s="10">
         <f>A22-'1.Припущення'!B30-A22*'1.Припущення'!B31</f>
@@ -1622,8 +1628,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="n">
-        <v>20000</v>
+      <c r="A23" s="15" t="n">
+        <v>70000</v>
       </c>
       <c r="B23" s="10">
         <f>A23-'1.Припущення'!B30-A23*'1.Припущення'!B31</f>
@@ -1644,7 +1650,7 @@
     </row>
     <row r="24">
       <c r="A24" s="8" t="n">
-        <v>29000</v>
+        <v>85000</v>
       </c>
       <c r="B24" s="10">
         <f>A24-'1.Припущення'!B30-A24*'1.Припущення'!B31</f>
@@ -1684,267 +1690,428 @@
     <row r="27">
       <c r="A27" s="22" t="inlineStr">
         <is>
-          <t>Ринок платить 13-20 тис. Для нуля при 70% завантаження потрібно ~29 тис. Розрив 1,8x.</t>
+          <t>За фактичною ставкою 70 000 грн бригада виходить у нуль на 53 дні (25% завантаження) навіть із новою УРБ у лізингу.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>C. IT-ІНЖЕНЕР — собівартість оплачуваної години</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="18" t="inlineStr">
-        <is>
-          <t>Повна вартість інженера, $/рік</t>
-        </is>
-      </c>
-      <c r="B31" s="23">
-        <f>'1.Припущення'!B35*12*(1+'1.Припущення'!B36+'1.Припущення'!B38)+'1.Припущення'!B37*12</f>
-        <v/>
+          <t>B2. ГЕОЛОГІЯ: результат за завантаженням (повна структура витрат)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Utilization</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Оплач. днів</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>Виручка</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>Витрати</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>ВАЛОВИЙ ПРИБУТОК</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>ВП на 1 FTE, $</t>
+        </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
-        <is>
-          <t>Собівартість 1 оплачуваної години, $</t>
-        </is>
-      </c>
-      <c r="B32" s="24">
-        <f>$B$31/'1.Припущення'!B8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Ринок збуту (тільки внутрішній)</t>
-        </is>
-      </c>
-      <c r="B33" s="3" t="inlineStr">
-        <is>
-          <t>Ставка $/год</t>
-        </is>
-      </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>ВП $/год</t>
-        </is>
-      </c>
-      <c r="D33" s="3" t="inlineStr">
-        <is>
-          <t>GM</t>
-        </is>
-      </c>
-      <c r="E33" s="3" t="inlineStr">
-        <is>
-          <t>ВП на інженера $/рік</t>
-        </is>
-      </c>
-      <c r="F33" s="3" t="inlineStr"/>
-      <c r="G33" s="3" t="inlineStr"/>
+      <c r="A32" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="B32" s="20">
+        <f>'1.Припущення'!B7*A32</f>
+        <v/>
+      </c>
+      <c r="C32" s="23">
+        <f>B32*'1.Припущення'!B24</f>
+        <v/>
+      </c>
+      <c r="D32" s="23">
+        <f>('1.Припущення'!B25+'1.Припущення'!B26+'1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29)+B32*'1.Припущення'!B30+C32*'1.Припущення'!B31</f>
+        <v/>
+      </c>
+      <c r="E32" s="15">
+        <f>C32-D32</f>
+        <v/>
+      </c>
+      <c r="F32" s="24">
+        <f>E32/C32</f>
+        <v/>
+      </c>
+      <c r="G32" s="23">
+        <f>E32/3.6/'1.Припущення'!B5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="B33" s="20">
+        <f>'1.Припущення'!B7*A33</f>
+        <v/>
+      </c>
+      <c r="C33" s="23">
+        <f>B33*'1.Припущення'!B24</f>
+        <v/>
+      </c>
+      <c r="D33" s="23">
+        <f>('1.Припущення'!B25+'1.Припущення'!B26+'1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29)+B33*'1.Припущення'!B30+C33*'1.Припущення'!B31</f>
+        <v/>
+      </c>
+      <c r="E33" s="15">
+        <f>C33-D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="24">
+        <f>E33/C33</f>
+        <v/>
+      </c>
+      <c r="G33" s="23">
+        <f>E33/3.6/'1.Припущення'!B5</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>Внутрішній UA, T&amp;M, сеньйорна команда</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="n">
-        <v>26</v>
-      </c>
-      <c r="C34" s="25">
-        <f>B34-$B$32</f>
-        <v/>
-      </c>
-      <c r="D34" s="16">
-        <f>C34/B34</f>
-        <v/>
-      </c>
-      <c r="E34" s="26">
-        <f>C34*'1.Припущення'!B8</f>
-        <v/>
-      </c>
-      <c r="F34" s="27" t="inlineStr">
-        <is>
-          <t>збиткова модель</t>
-        </is>
+      <c r="A34" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="B34" s="20">
+        <f>'1.Припущення'!B7*A34</f>
+        <v/>
+      </c>
+      <c r="C34" s="23">
+        <f>B34*'1.Припущення'!B24</f>
+        <v/>
+      </c>
+      <c r="D34" s="23">
+        <f>('1.Припущення'!B25+'1.Припущення'!B26+'1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29)+B34*'1.Припущення'!B30+C34*'1.Припущення'!B31</f>
+        <v/>
+      </c>
+      <c r="E34" s="15">
+        <f>C34-D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="24">
+        <f>E34/C34</f>
+        <v/>
+      </c>
+      <c r="G34" s="23">
+        <f>E34/3.6/'1.Припущення'!B5</f>
+        <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>Внутрішній UA, держ- і донорські проєкти</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="n">
-        <v>38</v>
-      </c>
-      <c r="C35" s="25">
-        <f>B35-$B$32</f>
-        <v/>
-      </c>
-      <c r="D35" s="16">
-        <f>C35/B35</f>
-        <v/>
-      </c>
-      <c r="E35" s="26">
-        <f>C35*'1.Припущення'!B8</f>
-        <v/>
-      </c>
-      <c r="F35" s="27" t="inlineStr">
-        <is>
-          <t>на межі нуля</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>Експортні ставки вилучено з моделі на вимогу власника.</t>
-        </is>
+      <c r="A35" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="B35" s="20">
+        <f>'1.Припущення'!B7*A35</f>
+        <v/>
+      </c>
+      <c r="C35" s="23">
+        <f>B35*'1.Припущення'!B24</f>
+        <v/>
+      </c>
+      <c r="D35" s="23">
+        <f>('1.Припущення'!B25+'1.Припущення'!B26+'1.Припущення'!B27+'1.Припущення'!B28+'1.Припущення'!B29)+B35*'1.Припущення'!B30+C35*'1.Припущення'!B31</f>
+        <v/>
+      </c>
+      <c r="E35" s="15">
+        <f>C35-D35</f>
+        <v/>
+      </c>
+      <c r="F35" s="24">
+        <f>E35/C35</f>
+        <v/>
+      </c>
+      <c r="G35" s="23">
+        <f>E35/3.6/'1.Припущення'!B5</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>D. ПІДПИСКИ — єдина модель, що дає маржу на внутрішньому ринку</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Модель</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>LTV $</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>LTV / CAC</t>
-        </is>
-      </c>
-      <c r="D39" s="3" t="inlineStr">
-        <is>
-          <t>CAC payback, міс</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>Клієнтів до беззбитковості</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t>Вердикт</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr"/>
+          <t>C. IT-ІНЖЕНЕР — собівартість оплачуваної години</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>Повна вартість інженера, $/рік</t>
+        </is>
+      </c>
+      <c r="B39" s="25">
+        <f>'1.Припущення'!B35*12*(1+'1.Припущення'!B36+'1.Припущення'!B38)+'1.Припущення'!B37*12</f>
+        <v/>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>D1 SaaS — мережі й інфраструктура</t>
-        </is>
-      </c>
-      <c r="B40" s="28">
-        <f>'1.Припущення'!B42*'1.Припущення'!C42/'1.Припущення'!E42</f>
-        <v/>
-      </c>
-      <c r="C40" s="29">
-        <f>B40/'1.Припущення'!D42</f>
-        <v/>
-      </c>
-      <c r="D40" s="29">
-        <f>'1.Припущення'!D42/('1.Припущення'!B42*'1.Припущення'!C42/12)</f>
-        <v/>
-      </c>
-      <c r="E40" s="30">
-        <f>(8*$B$31+60000)/('1.Припущення'!B42*'1.Припущення'!C42)</f>
-        <v/>
-      </c>
-      <c r="F40" s="31" t="inlineStr">
-        <is>
-          <t>ІНВЕСТУВАТИ</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>D2 DaaS-моніторинг обʼєкта</t>
-        </is>
-      </c>
-      <c r="B41" s="28">
-        <f>'1.Припущення'!B43*'1.Припущення'!C43/'1.Припущення'!E43</f>
-        <v/>
-      </c>
-      <c r="C41" s="29">
-        <f>B41/'1.Припущення'!D43</f>
-        <v/>
-      </c>
-      <c r="D41" s="29">
-        <f>'1.Припущення'!D43/('1.Припущення'!B43*'1.Припущення'!C43/12)</f>
-        <v/>
-      </c>
-      <c r="E41" s="30">
-        <f>(3*$B$31+20000)/('1.Припущення'!B43*'1.Припущення'!C43)</f>
-        <v/>
-      </c>
-      <c r="F41" s="31" t="inlineStr">
-        <is>
-          <t>ІНВЕСТУВАТИ</t>
-        </is>
-      </c>
+      <c r="A40" s="18" t="inlineStr">
+        <is>
+          <t>Собівартість 1 оплачуваної години, $</t>
+        </is>
+      </c>
+      <c r="B40" s="26">
+        <f>$B$39/'1.Припущення'!B8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Ринок збуту (тільки внутрішній)</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="inlineStr">
+        <is>
+          <t>Ставка $/год</t>
+        </is>
+      </c>
+      <c r="C41" s="3" t="inlineStr">
+        <is>
+          <t>ВП $/год</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>ВП на інженера $/рік</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
+          <t>Внутрішній UA, T&amp;M, сеньйорна команда</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>26</v>
+      </c>
+      <c r="C42" s="27">
+        <f>B42-$B$40</f>
+        <v/>
+      </c>
+      <c r="D42" s="16">
+        <f>C42/B42</f>
+        <v/>
+      </c>
+      <c r="E42" s="28">
+        <f>C42*'1.Припущення'!B8</f>
+        <v/>
+      </c>
+      <c r="F42" s="29" t="inlineStr">
+        <is>
+          <t>збиткова модель</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Внутрішній UA, держ- і донорські проєкти</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="C43" s="27">
+        <f>B43-$B$40</f>
+        <v/>
+      </c>
+      <c r="D43" s="16">
+        <f>C43/B43</f>
+        <v/>
+      </c>
+      <c r="E43" s="28">
+        <f>C43*'1.Припущення'!B8</f>
+        <v/>
+      </c>
+      <c r="F43" s="29" t="inlineStr">
+        <is>
+          <t>на межі нуля</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Експортні ставки вилучено з моделі на вимогу власника.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>D. ПІДПИСКИ — єдина модель, що дає маржу на внутрішньому ринку</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Модель</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>LTV $</t>
+        </is>
+      </c>
+      <c r="C47" s="3" t="inlineStr">
+        <is>
+          <t>LTV / CAC</t>
+        </is>
+      </c>
+      <c r="D47" s="3" t="inlineStr">
+        <is>
+          <t>CAC payback, міс</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>Клієнтів до беззбитковості</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>Вердикт</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>D1 SaaS — мережі й інфраструктура</t>
+        </is>
+      </c>
+      <c r="B48" s="23">
+        <f>'1.Припущення'!B42*'1.Припущення'!C42/'1.Припущення'!E42</f>
+        <v/>
+      </c>
+      <c r="C48" s="30">
+        <f>B48/'1.Припущення'!D42</f>
+        <v/>
+      </c>
+      <c r="D48" s="30">
+        <f>'1.Припущення'!D42/('1.Припущення'!B42*'1.Припущення'!C42/12)</f>
+        <v/>
+      </c>
+      <c r="E48" s="20">
+        <f>(8*$B$39+60000)/('1.Припущення'!B42*'1.Припущення'!C42)</f>
+        <v/>
+      </c>
+      <c r="F48" s="31" t="inlineStr">
+        <is>
+          <t>ІНВЕСТУВАТИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>D2 DaaS-моніторинг обʼєкта</t>
+        </is>
+      </c>
+      <c r="B49" s="23">
+        <f>'1.Припущення'!B43*'1.Припущення'!C43/'1.Припущення'!E43</f>
+        <v/>
+      </c>
+      <c r="C49" s="30">
+        <f>B49/'1.Припущення'!D43</f>
+        <v/>
+      </c>
+      <c r="D49" s="30">
+        <f>'1.Припущення'!D43/('1.Припущення'!B43*'1.Припущення'!C43/12)</f>
+        <v/>
+      </c>
+      <c r="E49" s="20">
+        <f>(3*$B$39+20000)/('1.Припущення'!B43*'1.Припущення'!C43)</f>
+        <v/>
+      </c>
+      <c r="F49" s="31" t="inlineStr">
+        <is>
+          <t>ІНВЕСТУВАТИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
           <t>D3 Агро-продукт</t>
         </is>
       </c>
-      <c r="B42" s="26">
+      <c r="B50" s="28">
         <f>'1.Припущення'!B44*'1.Припущення'!C44/'1.Припущення'!E44</f>
         <v/>
       </c>
-      <c r="C42" s="25">
-        <f>B42/'1.Припущення'!D44</f>
-        <v/>
-      </c>
-      <c r="D42" s="25">
+      <c r="C50" s="27">
+        <f>B50/'1.Припущення'!D44</f>
+        <v/>
+      </c>
+      <c r="D50" s="27">
         <f>'1.Припущення'!D44/('1.Припущення'!B44*'1.Припущення'!C44/12)</f>
         <v/>
       </c>
-      <c r="E42" s="20">
-        <f>(8*$B$31+60000)/('1.Припущення'!B44*'1.Припущення'!C44)</f>
-        <v/>
-      </c>
-      <c r="F42" s="27" t="inlineStr">
+      <c r="E50" s="32">
+        <f>(8*$B$39+60000)/('1.Припущення'!B44*'1.Припущення'!C44)</f>
+        <v/>
+      </c>
+      <c r="F50" s="29" t="inlineStr">
         <is>
           <t>НІ — payback 30 міс</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>Орієнтир здорової моделі: LTV/CAC &gt; 3, payback &lt; 12 міс.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A30:H30"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A38:H38"/>
     <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A46:H46"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2055,35 +2222,35 @@
           <t>M6  Мережі й комунальна інфраструктура</t>
         </is>
       </c>
-      <c r="B5" s="28" t="n">
+      <c r="B5" s="23" t="n">
         <v>950</v>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="23" t="n">
         <v>1159</v>
       </c>
-      <c r="D5" s="28" t="n">
+      <c r="D5" s="23" t="n">
         <v>1437</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="23" t="n">
         <v>1753</v>
       </c>
-      <c r="F5" s="28" t="n">
+      <c r="F5" s="23" t="n">
         <v>614</v>
       </c>
-      <c r="G5" s="28" t="n">
+      <c r="G5" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="23" t="n">
         <v>80</v>
       </c>
       <c r="I5" s="17" t="n">
         <v>0.62</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="23">
         <f>H5*I5</f>
         <v/>
       </c>
-      <c r="K5" s="30" t="n">
+      <c r="K5" s="20" t="n">
         <v>23</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -2098,35 +2265,35 @@
           <t>M5  Дорожники та інфраструктура</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="23" t="n">
         <v>650</v>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="23" t="n">
         <v>767</v>
       </c>
-      <c r="D6" s="28" t="n">
+      <c r="D6" s="23" t="n">
         <v>959</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="23" t="n">
         <v>1189</v>
       </c>
-      <c r="F6" s="28" t="n">
+      <c r="F6" s="23" t="n">
         <v>357</v>
       </c>
-      <c r="G6" s="28" t="n">
+      <c r="G6" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="23" t="n">
         <v>46</v>
       </c>
       <c r="I6" s="17" t="n">
         <v>0.52</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="23">
         <f>H6*I6</f>
         <v/>
       </c>
-      <c r="K6" s="30" t="n">
+      <c r="K6" s="20" t="n">
         <v>14</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -2136,45 +2303,45 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>M1  Топографо-геодезичні вишукування</t>
         </is>
       </c>
-      <c r="B7" s="10" t="n">
+      <c r="B7" s="28" t="n">
         <v>2860</v>
       </c>
-      <c r="C7" s="10" t="n">
+      <c r="C7" s="28" t="n">
         <v>3089</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="28" t="n">
         <v>3367</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="28" t="n">
         <v>3636</v>
       </c>
-      <c r="F7" s="10" t="n">
+      <c r="F7" s="28" t="n">
         <v>1236</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <v>87</v>
-      </c>
-      <c r="I7" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="J7" s="10">
+      <c r="G7" s="28" t="n">
+        <v>20</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>22</v>
+      </c>
+      <c r="I7" s="16" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J7" s="28">
         <f>H7*I7</f>
         <v/>
       </c>
-      <c r="K7" s="11" t="n">
-        <v>33</v>
+      <c r="K7" s="32" t="n">
+        <v>20</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>базовий обсяг; зростання лише інфляційне</t>
+          <t>$6 796 на людину — найнижчий показник портфеля</t>
         </is>
       </c>
     </row>
@@ -2184,35 +2351,35 @@
           <t>M9  Надра й карʼєри: маркшейдерія + DaaS</t>
         </is>
       </c>
-      <c r="B8" s="28" t="n">
+      <c r="B8" s="23" t="n">
         <v>380</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="23" t="n">
         <v>426</v>
       </c>
-      <c r="D8" s="28" t="n">
+      <c r="D8" s="23" t="n">
         <v>481</v>
       </c>
-      <c r="E8" s="28" t="n">
+      <c r="E8" s="23" t="n">
         <v>534</v>
       </c>
-      <c r="F8" s="28" t="n">
+      <c r="F8" s="23" t="n">
         <v>240</v>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="G8" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="23" t="n">
         <v>22</v>
       </c>
       <c r="I8" s="17" t="n">
         <v>0.66</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="23">
         <f>H8*I8</f>
         <v/>
       </c>
-      <c r="K8" s="30" t="n">
+      <c r="K8" s="20" t="n">
         <v>7</v>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -2308,40 +2475,40 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="27" t="inlineStr">
+      <c r="A11" s="29" t="inlineStr">
         <is>
           <t>M4  ІТ / цифра для агро</t>
         </is>
       </c>
-      <c r="B11" s="26" t="n">
+      <c r="B11" s="28" t="n">
         <v>3890</v>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="28" t="n">
         <v>4435</v>
       </c>
-      <c r="D11" s="26" t="n">
+      <c r="D11" s="28" t="n">
         <v>5055</v>
       </c>
-      <c r="E11" s="26" t="n">
+      <c r="E11" s="28" t="n">
         <v>5713</v>
       </c>
-      <c r="F11" s="26" t="n">
+      <c r="F11" s="28" t="n">
         <v>457</v>
       </c>
-      <c r="G11" s="26" t="n">
+      <c r="G11" s="28" t="n">
         <v>8</v>
       </c>
-      <c r="H11" s="26" t="n">
+      <c r="H11" s="28" t="n">
         <v>27</v>
       </c>
       <c r="I11" s="16" t="n">
         <v>0.6</v>
       </c>
-      <c r="J11" s="26">
+      <c r="J11" s="28">
         <f>H11*I11</f>
         <v/>
       </c>
-      <c r="K11" s="20" t="n">
+      <c r="K11" s="32" t="n">
         <v>8</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -2351,83 +2518,83 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="31" t="inlineStr">
         <is>
           <t>M2  Інженерно-геологічні вишукування</t>
         </is>
       </c>
-      <c r="B12" s="26" t="n">
+      <c r="B12" s="23" t="n">
         <v>2410</v>
       </c>
-      <c r="C12" s="26" t="n">
+      <c r="C12" s="23" t="n">
         <v>2579</v>
       </c>
-      <c r="D12" s="26" t="n">
+      <c r="D12" s="23" t="n">
         <v>2785</v>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="23" t="n">
         <v>2980</v>
       </c>
-      <c r="F12" s="26" t="n">
+      <c r="F12" s="23" t="n">
         <v>894</v>
       </c>
-      <c r="G12" s="26" t="n">
-        <v>22</v>
-      </c>
-      <c r="H12" s="26" t="n">
-        <v>45</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="J12" s="26">
+      <c r="G12" s="23" t="n">
+        <v>27</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>82</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J12" s="23">
         <f>H12*I12</f>
         <v/>
       </c>
       <c r="K12" s="20" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>беззбитковість недосяжна за ринковою ціною</t>
+          <t>ФАКТ 70 000 грн/день: GM 52%, обмежує капітал</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="29" t="inlineStr">
         <is>
           <t>M7  Громади / містобудівна документація</t>
         </is>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="28" t="n">
         <v>750</v>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="28" t="n">
         <v>825</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="28" t="n">
         <v>916</v>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="28" t="n">
         <v>1007</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="28" t="n">
         <v>252</v>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="H13" s="26" t="n">
+      <c r="H13" s="28" t="n">
         <v>9</v>
       </c>
       <c r="I13" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="J13" s="26">
+      <c r="J13" s="28">
         <f>H13*I13</f>
         <v/>
       </c>
-      <c r="K13" s="20" t="n">
+      <c r="K13" s="32" t="n">
         <v>3</v>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -2437,53 +2604,53 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="32" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>РАЗОМ</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="34">
         <f>SUM(B5:B13)</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="34">
         <f>SUM(C5:C13)</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="34">
         <f>SUM(D5:D13)</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="34">
         <f>SUM(E5:E13)</f>
         <v/>
       </c>
-      <c r="F14" s="33">
+      <c r="F14" s="34">
         <f>SUM(F5:F13)</f>
         <v/>
       </c>
-      <c r="G14" s="33">
+      <c r="G14" s="34">
         <f>SUM(G5:G13)</f>
         <v/>
       </c>
-      <c r="H14" s="33">
+      <c r="H14" s="34">
         <f>SUM(H5:H13)</f>
         <v/>
       </c>
-      <c r="I14" s="32" t="n"/>
-      <c r="J14" s="33">
+      <c r="I14" s="33" t="n"/>
+      <c r="J14" s="34">
         <f>SUM(J5:J13)</f>
         <v/>
       </c>
-      <c r="K14" s="34">
+      <c r="K14" s="35">
         <f>SUM(K5:K13)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>Увесь внутрішній SOM потребує ~115 людей при плані 100. Без експорту кожна відмова прямо зменшує виручку — компенсувати нічим.</t>
+      <c r="A16" s="36" t="inlineStr">
+        <is>
+          <t>Увесь внутрішній SOM потребує ~117 людей при плані 100. Геологія (M2) піднялась із останнього місця на друге за абсолютним валовим прибутком.</t>
         </is>
       </c>
     </row>
@@ -2604,22 +2771,22 @@
           <t>M6  Мережі й комунальна інфра</t>
         </is>
       </c>
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="37">
         <f>SUMPRODUCT(B6:F6,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -2640,22 +2807,22 @@
           <t>M5  Дорожники та інфраструктура</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n">
+      <c r="B7" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="30" t="n">
+      <c r="C7" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="30" t="n">
+      <c r="E7" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="30" t="n">
+      <c r="F7" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="35">
+      <c r="G7" s="37">
         <f>SUMPRODUCT(B7:F7,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -2676,22 +2843,22 @@
           <t>M9  Надра/карʼєри: DaaS-обʼєми</t>
         </is>
       </c>
-      <c r="B8" s="30" t="n">
+      <c r="B8" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="30" t="n">
+      <c r="C8" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="30" t="n">
+      <c r="D8" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="30" t="n">
+      <c r="E8" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="F8" s="30" t="n">
+      <c r="F8" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="35">
+      <c r="G8" s="37">
         <f>SUMPRODUCT(B8:F8,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -2713,7 +2880,7 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>1</v>
@@ -2727,18 +2894,18 @@
       <c r="F9" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="36">
+      <c r="G9" s="38">
         <f>SUMPRODUCT(B9:F9,$B$5:$F$5)</f>
         <v/>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>● КЕШ + КАНАЛ</t>
+          <t>● ТІЛЬКИ КАНАЛ</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>33 людини заради 23 млн ВП, але робить CAC підписки $1 800</t>
+          <t>$4 222 на людину; цінність — у CAC підписки $1 800 замість $8 500</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2930,7 @@
       <c r="F10" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="36">
+      <c r="G10" s="38">
         <f>SUMPRODUCT(B10:F10,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -2799,7 +2966,7 @@
       <c r="F11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="38">
         <f>SUMPRODUCT(B11:F11,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -2815,108 +2982,108 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="inlineStr">
+      <c r="A12" s="29" t="inlineStr">
         <is>
           <t>M4  ІТ / цифра для агро</t>
         </is>
       </c>
-      <c r="B12" s="20" t="n">
+      <c r="B12" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="20" t="n">
+      <c r="C12" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="D12" s="20" t="n">
+      <c r="D12" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="E12" s="20" t="n">
+      <c r="E12" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="20" t="n">
+      <c r="F12" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="37">
+      <c r="G12" s="39">
         <f>SUMPRODUCT(B12:F12,$B$5:$F$5)</f>
         <v/>
       </c>
-      <c r="H12" s="27" t="inlineStr">
+      <c r="H12" s="29" t="inlineStr">
         <is>
           <t>✗ НІ</t>
         </is>
       </c>
-      <c r="I12" s="27" t="inlineStr">
+      <c r="I12" s="29" t="inlineStr">
         <is>
           <t>LTV/CAC 1,8, payback 30,5 міс — ринок зайнятий</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="27" t="inlineStr">
+      <c r="A13" s="31" t="inlineStr">
         <is>
           <t>M2  Інженерно-геологічні вишукування</t>
         </is>
       </c>
       <c r="B13" s="20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C13" s="20" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D13" s="20" t="n">
         <v>5</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" s="37">
         <f>SUMPRODUCT(B13:F13,$B$5:$F$5)</f>
         <v/>
       </c>
-      <c r="H13" s="27" t="inlineStr">
-        <is>
-          <t>✗ ЗМІНИТИ РОЛЬ</t>
-        </is>
-      </c>
-      <c r="I13" s="27" t="inlineStr">
-        <is>
-          <t>беззбитковість недосяжна: треба 29 тис./день, ринок дає 16 тис.</t>
+      <c r="H13" s="31" t="inlineStr">
+        <is>
+          <t>★★★ ЯДРО</t>
+        </is>
+      </c>
+      <c r="I13" s="31" t="inlineStr">
+        <is>
+          <t>ФАКТ 70 000 грн/день: GM 52%, окупність УРБ менш ніж рік</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>M7  Громади / містобудівна докум.</t>
         </is>
       </c>
-      <c r="B14" s="20" t="n">
+      <c r="B14" s="32" t="n">
         <v>1</v>
       </c>
-      <c r="C14" s="20" t="n">
+      <c r="C14" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="20" t="n">
+      <c r="D14" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="20" t="n">
+      <c r="E14" s="32" t="n">
         <v>3</v>
       </c>
-      <c r="F14" s="20" t="n">
+      <c r="F14" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="39">
         <f>SUMPRODUCT(B14:F14,$B$5:$F$5)</f>
         <v/>
       </c>
-      <c r="H14" s="27" t="inlineStr">
+      <c r="H14" s="29" t="inlineStr">
         <is>
           <t>✗ НІ</t>
         </is>
       </c>
-      <c r="I14" s="27" t="inlineStr">
+      <c r="I14" s="29" t="inlineStr">
         <is>
           <t>тендери, демпінг, дрібні чеки</t>
         </is>
@@ -2936,7 +3103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -2956,7 +3123,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="40" t="inlineStr">
         <is>
           <t>База 2026 — реконструкція за РИНКОВИМИ цінами і «легкою» структурою витрат, НЕ ваша звітність.</t>
         </is>
@@ -3009,19 +3176,19 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Топогеодезія</t>
+          <t>Геологія (3,3 бригади, util 55%)</t>
         </is>
       </c>
       <c r="B6" s="11" t="n">
-        <v>22</v>
-      </c>
-      <c r="C6" s="39" t="n">
-        <v>62</v>
+        <v>12</v>
+      </c>
+      <c r="C6" s="41" t="n">
+        <v>26.9</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E6" s="39">
+        <v>0.44</v>
+      </c>
+      <c r="E6" s="41">
         <f>C6*D6</f>
         <v/>
       </c>
@@ -3031,26 +3198,26 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>util ~62%, ставка 14 000 грн/день, «легка» структура</t>
+          <t>ФАКТ 70 000 грн/день — увесь прибуток компанії</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Геологія (буріння)</t>
+          <t>Топогеодезія (9,2 бригади, util 62%)</t>
         </is>
       </c>
       <c r="B7" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C7" s="39" t="n">
-        <v>30</v>
+        <v>22</v>
+      </c>
+      <c r="C7" s="41" t="n">
+        <v>19.6</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="E7" s="39">
+        <v>0.21</v>
+      </c>
+      <c r="E7" s="41">
         <f>C7*D7</f>
         <v/>
       </c>
@@ -3060,7 +3227,7 @@
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>нижче точки беззбитковості за ринковою ціною</t>
+          <t>15 000 грн/день, «легка» структура витрат</t>
         </is>
       </c>
     </row>
@@ -3073,13 +3240,13 @@
       <c r="B8" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="39" t="n">
+      <c r="C8" s="41" t="n">
         <v>17</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="E8" s="39">
+      <c r="E8" s="41">
         <f>C8*D8</f>
         <v/>
       </c>
@@ -3102,13 +3269,13 @@
       <c r="B9" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="39" t="n">
+      <c r="C9" s="41" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="39">
+      <c r="E9" s="41">
         <f>C9*D9</f>
         <v/>
       </c>
@@ -3119,32 +3286,32 @@
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="32" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>РАЗОМ</t>
         </is>
       </c>
-      <c r="B10" s="32">
+      <c r="B10" s="33">
         <f>SUM(B6:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="40">
+      <c r="C10" s="42">
         <f>SUM(C6:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="41">
+      <c r="D10" s="43">
         <f>E10/C10</f>
         <v/>
       </c>
-      <c r="E10" s="40">
+      <c r="E10" s="42">
         <f>SUM(E6:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="34">
         <f>E10*1000000/45.0/B10</f>
         <v/>
       </c>
-      <c r="G10" s="32" t="inlineStr"/>
+      <c r="G10" s="33" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
@@ -3155,7 +3322,7 @@
       <c r="B11" s="9" t="n">
         <v>0.16</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="44">
         <f>C10*B11</f>
         <v/>
       </c>
@@ -3166,21 +3333,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="32" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>EBITDA, млн грн</t>
         </is>
       </c>
-      <c r="B12" s="43" t="n"/>
-      <c r="C12" s="40">
+      <c r="B12" s="45" t="n"/>
+      <c r="C12" s="42">
         <f>E10-C11</f>
         <v/>
       </c>
-      <c r="D12" s="44">
+      <c r="D12" s="46">
         <f>C12/C10</f>
         <v/>
       </c>
-      <c r="E12" s="45">
+      <c r="E12" s="47">
         <f>C12*1000000/45.0</f>
         <v/>
       </c>
@@ -3237,19 +3404,19 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Мережі / комунальна інфра: продукт + підписка</t>
+          <t>Геологія (8 бригад, util 70%)</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="C16" s="39" t="n">
-        <v>65</v>
+        <v>29</v>
+      </c>
+      <c r="C16" s="41" t="n">
+        <v>82.3</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E16" s="39">
+        <v>0.518</v>
+      </c>
+      <c r="E16" s="41">
         <f>C16*D16</f>
         <v/>
       </c>
@@ -3259,26 +3426,26 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>~90 ентерпрайз-акаунтів</t>
+          <t>СТАВКА 1: обмежує капітал ~$450 тис. на 5 УРБ</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Топогеодезія (кеш + канал продажів)</t>
+          <t>Мережі / комунальна інфра: продукт + підписка</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>33</v>
-      </c>
-      <c r="C17" s="39" t="n">
-        <v>87</v>
+        <v>20</v>
+      </c>
+      <c r="C17" s="41" t="n">
+        <v>65</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E17" s="39">
+        <v>0.62</v>
+      </c>
+      <c r="E17" s="41">
         <f>C17*D17</f>
         <v/>
       </c>
@@ -3288,7 +3455,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>«легка» структура + util 75% + чек 50 тис.</t>
+          <t>СТАВКА 2: ~90 ентерпрайз-акаунтів</t>
         </is>
       </c>
     </row>
@@ -3299,15 +3466,15 @@
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C18" s="39" t="n">
-        <v>46</v>
+        <v>12</v>
+      </c>
+      <c r="C18" s="41" t="n">
+        <v>40</v>
       </c>
       <c r="D18" s="12" t="n">
         <v>0.52</v>
       </c>
-      <c r="E18" s="39">
+      <c r="E18" s="41">
         <f>C18*D18</f>
         <v/>
       </c>
@@ -3317,7 +3484,7 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>донорські інфрапроєкти</t>
+          <t>СТАВКА 3: донорські інфрапроєкти</t>
         </is>
       </c>
     </row>
@@ -3330,13 +3497,13 @@
       <c r="B19" s="11" t="n">
         <v>7</v>
       </c>
-      <c r="C19" s="39" t="n">
+      <c r="C19" s="41" t="n">
         <v>21</v>
       </c>
       <c r="D19" s="12" t="n">
         <v>0.66</v>
       </c>
-      <c r="E19" s="39">
+      <c r="E19" s="41">
         <f>C19*D19</f>
         <v/>
       </c>
@@ -3346,26 +3513,26 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>та сама технологія, що й дороги</t>
+          <t>СТАВКА 3: та сама технологія, що й дороги</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>ІТ для будівельників (BIM / ЄДЕССБ)</t>
+          <t>Топогеодезія (8,3 бригади — канал продажів)</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="C20" s="39" t="n">
-        <v>28</v>
+        <v>20</v>
+      </c>
+      <c r="C20" s="41" t="n">
+        <v>21.6</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E20" s="39">
+        <v>0.336</v>
+      </c>
+      <c r="E20" s="41">
         <f>C20*D20</f>
         <v/>
       </c>
@@ -3375,26 +3542,26 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>продукт, не години</t>
+          <t>не росте; робить CAC підписки $1 800</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Розмінування: геодані + звітність</t>
+          <t>Адмін / продажі / маркетинг / R&amp;D</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" s="39" t="n">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="C21" s="41" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E21" s="39">
+        <v>0</v>
+      </c>
+      <c r="E21" s="41">
         <f>C21*D21</f>
         <v/>
       </c>
@@ -3402,166 +3569,137 @@
         <f>IF(B21=0,0,E21*1000000/51.5/B21)</f>
         <v/>
       </c>
-      <c r="G21" s="4" t="inlineStr">
-        <is>
-          <t>опція, не ставка</t>
-        </is>
-      </c>
+      <c r="G21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>Адмін / продажі / маркетинг / R&amp;D</t>
-        </is>
-      </c>
-      <c r="B22" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="C22" s="39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="39">
-        <f>C22*D22</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>IF(B22=0,0,E22*1000000/51.5/B22)</f>
-        <v/>
-      </c>
-      <c r="G22" s="4" t="inlineStr"/>
+      <c r="A22" s="33" t="inlineStr">
+        <is>
+          <t>РАЗОМ</t>
+        </is>
+      </c>
+      <c r="B22" s="33">
+        <f>SUM(B16:B21)</f>
+        <v/>
+      </c>
+      <c r="C22" s="42">
+        <f>SUM(C16:C21)</f>
+        <v/>
+      </c>
+      <c r="D22" s="43">
+        <f>E22/C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="42">
+        <f>SUM(E16:E21)</f>
+        <v/>
+      </c>
+      <c r="F22" s="34">
+        <f>E22*1000000/51.5/B22</f>
+        <v/>
+      </c>
+      <c r="G22" s="33" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="32" t="inlineStr">
-        <is>
-          <t>РАЗОМ</t>
-        </is>
-      </c>
-      <c r="B23" s="32">
-        <f>SUM(B16:B22)</f>
-        <v/>
-      </c>
-      <c r="C23" s="40">
-        <f>SUM(C16:C22)</f>
-        <v/>
-      </c>
-      <c r="D23" s="41">
-        <f>E23/C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="40">
-        <f>SUM(E16:E22)</f>
-        <v/>
-      </c>
-      <c r="F23" s="33">
-        <f>E23*1000000/51.5/B23</f>
-        <v/>
-      </c>
-      <c r="G23" s="32" t="inlineStr"/>
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>SG&amp;A, % від виручки</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C23" s="44">
+        <f>C22*B23</f>
+        <v/>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>вище, бо зʼявляються продажі й маркетинг продукту</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
-        <is>
-          <t>SG&amp;A, % від виручки</t>
-        </is>
-      </c>
-      <c r="B24" s="9" t="n">
-        <v>0.27</v>
-      </c>
+      <c r="A24" s="33" t="inlineStr">
+        <is>
+          <t>EBITDA, млн грн</t>
+        </is>
+      </c>
+      <c r="B24" s="45" t="n"/>
       <c r="C24" s="42">
-        <f>C23*B24</f>
-        <v/>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>вище, бо зʼявляються продажі й маркетинг продукту</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="32" t="inlineStr">
-        <is>
-          <t>EBITDA, млн грн</t>
-        </is>
-      </c>
-      <c r="B25" s="43" t="n"/>
-      <c r="C25" s="40">
-        <f>E23-C24</f>
-        <v/>
-      </c>
-      <c r="D25" s="44">
-        <f>C25/C23</f>
-        <v/>
-      </c>
-      <c r="E25" s="45">
-        <f>C25*1000000/51.5</f>
-        <v/>
-      </c>
-      <c r="F25" t="inlineStr">
+        <f>E22-C23</f>
+        <v/>
+      </c>
+      <c r="D24" s="46">
+        <f>C24/C22</f>
+        <v/>
+      </c>
+      <c r="E24" s="47">
+        <f>C24*1000000/51.5</f>
+        <v/>
+      </c>
+      <c r="F24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t>ДЕЛЬТА 2026 → 2029</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="46" t="inlineStr">
-        <is>
-          <t>ДЕЛЬТА 2026 → 2029</t>
-        </is>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>Виручка</t>
+        </is>
+      </c>
+      <c r="B27" s="49">
+        <f>C22/C10</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Виручка</t>
-        </is>
-      </c>
-      <c r="B28" s="47">
-        <f>C23/C10</f>
+          <t>Валовий прибуток</t>
+        </is>
+      </c>
+      <c r="B28" s="49">
+        <f>E22/E10</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Валовий прибуток</t>
-        </is>
-      </c>
-      <c r="B29" s="47">
-        <f>E23/E10</f>
+          <t>Валовий прибуток на 1 FTE</t>
+        </is>
+      </c>
+      <c r="B29" s="49">
+        <f>F22/F10</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Валовий прибуток на 1 FTE</t>
-        </is>
-      </c>
-      <c r="B30" s="47">
-        <f>F23/F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
           <t>EBITDA, млн грн</t>
         </is>
       </c>
-      <c r="B31" s="42">
+      <c r="B30" s="44">
         <f>C12</f>
         <v/>
       </c>
-      <c r="C31" s="48" t="inlineStr">
+      <c r="C30" s="50" t="inlineStr">
         <is>
           <t>→</t>
         </is>
       </c>
-      <c r="D31" s="49">
-        <f>C25</f>
+      <c r="D30" s="51">
+        <f>C24</f>
         <v/>
       </c>
     </row>
@@ -3600,7 +3738,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="inlineStr">
+      <c r="A2" s="40" t="inlineStr">
         <is>
           <t>Без експорту всі шість напрямків живляться з одного джерела: бюджету й донорських грошей.</t>
         </is>
@@ -3647,15 +3785,15 @@
       <c r="B5" s="9" t="n">
         <v>0.55</v>
       </c>
-      <c r="C5" s="50" t="n">
+      <c r="C5" s="52" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="10">
-        <f>(65+87+46+21+28+13)*C5</f>
+        <f>(82.3+65+40+21+21.6)*C5</f>
         <v/>
       </c>
       <c r="E5" s="10">
-        <f>(65*0.62+87*0.26+46*0.52+21*0.66+28*0.45+13*0.55)*C5-D5*0.27</f>
+        <f>(82.3*0.518+65*0.62+40*0.52+21*0.66+21.6*0.336)*C5-D5*0.27</f>
         <v/>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -3673,15 +3811,15 @@
       <c r="B6" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="C6" s="50" t="n">
+      <c r="C6" s="52" t="n">
         <v>1.85</v>
       </c>
       <c r="D6" s="10">
-        <f>(65+87+46+21+28+13)*C6</f>
+        <f>(82.3+65+40+21+21.6)*C6</f>
         <v/>
       </c>
       <c r="E6" s="10">
-        <f>(65*0.62+87*0.26+46*0.52+21*0.66+28*0.45+13*0.55)*C6-D6*0.27</f>
+        <f>(82.3*0.518+65*0.62+40*0.52+21*0.66+21.6*0.336)*C6-D6*0.27</f>
         <v/>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -3691,7 +3829,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="27" t="inlineStr">
+      <c r="A7" s="29" t="inlineStr">
         <is>
           <t>C. Ескалація / зрив фінансування</t>
         </is>
@@ -3699,42 +3837,42 @@
       <c r="B7" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="C7" s="51" t="n">
+      <c r="C7" s="53" t="n">
         <v>0.5</v>
       </c>
-      <c r="D7" s="26">
-        <f>(65+87+46+21+28+13)*C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="26">
-        <f>(65*0.62+87*0.26+46*0.52+21*0.66+28*0.45+13*0.55)*C7-D7*0.27</f>
-        <v/>
-      </c>
-      <c r="F7" s="27" t="inlineStr">
+      <c r="D7" s="28">
+        <f>(82.3+65+40+21+21.6)*C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>(82.3*0.518+65*0.62+40*0.52+21*0.66+21.6*0.336)*C7-D7*0.27</f>
+        <v/>
+      </c>
+      <c r="F7" s="29" t="inlineStr">
         <is>
           <t>виручка падає удвічі — нижню межу не тримає ніщо</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="32" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>ОЧІКУВАНЕ ЗНАЧЕННЯ (зважене)</t>
         </is>
       </c>
-      <c r="B8" s="32" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="33">
+      <c r="B8" s="33" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="34">
         <f>SUMPRODUCT(B5:B7,D5:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <f>SUMPRODUCT(B5:B7,E5:E7)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>Раніше експорт тримав нижню межу: внутрішні ринки падали на 45%, валютна лінія майже ні. Тепер такої лінії немає.</t>
         </is>

--- a/market-analysis/unit-economics-model.xlsx
+++ b/market-analysis/unit-economics-model.xlsx
@@ -13,6 +13,7 @@
     <sheet name="4.Матриця рішення" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="5.P&amp;L 2026-2029" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="6.Сценарії" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7.Чотири ринки" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="0.0&quot;x&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -56,6 +57,11 @@
     <font>
       <b val="1"/>
       <color rgb="001F3864"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -131,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -167,14 +173,15 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -182,7 +189,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -190,6 +197,7 @@
     <xf numFmtId="166" fontId="4" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2123,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -2219,72 +2227,72 @@
     <row r="5">
       <c r="A5" s="31" t="inlineStr">
         <is>
-          <t>M6  Мережі й комунальна інфраструктура</t>
+          <t>R4  ІТ-розробка для індустрій</t>
         </is>
       </c>
       <c r="B5" s="23" t="n">
-        <v>950</v>
+        <v>3226</v>
       </c>
       <c r="C5" s="23" t="n">
-        <v>1159</v>
+        <v>3871</v>
       </c>
       <c r="D5" s="23" t="n">
-        <v>1437</v>
+        <v>4645</v>
       </c>
       <c r="E5" s="23" t="n">
-        <v>1753</v>
+        <v>5570</v>
       </c>
       <c r="F5" s="23" t="n">
-        <v>614</v>
+        <v>1392</v>
       </c>
       <c r="G5" s="23" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H5" s="23" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="I5" s="17" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="J5" s="23">
         <f>H5*I5</f>
         <v/>
       </c>
       <c r="K5" s="20" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
-          <t>RDNA5: енергетика в топ-3 збитків; донори вимагають облік активів</t>
+          <t>двигун зростання; ядро — мережі. ROIC 957%</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>M5  Дорожники та інфраструктура</t>
+          <t>R2  Інженерна геологія</t>
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>650</v>
+        <v>2410</v>
       </c>
       <c r="C6" s="23" t="n">
-        <v>767</v>
+        <v>2579</v>
       </c>
       <c r="D6" s="23" t="n">
-        <v>959</v>
+        <v>2785</v>
       </c>
       <c r="E6" s="23" t="n">
-        <v>1189</v>
+        <v>2980</v>
       </c>
       <c r="F6" s="23" t="n">
-        <v>357</v>
+        <v>894</v>
       </c>
       <c r="G6" s="23" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="H6" s="23" t="n">
-        <v>46</v>
+        <v>74</v>
       </c>
       <c r="I6" s="17" t="n">
         <v>0.52</v>
@@ -2294,363 +2302,420 @@
         <v/>
       </c>
       <c r="K6" s="20" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>дорфонд 12,6 млрд при потребі 52 млрд; донори</t>
+          <t>грошова корова: LTV/CAC 39, payback 0,9 міс</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
-        <is>
-          <t>M1  Топографо-геодезичні вишукування</t>
-        </is>
-      </c>
-      <c r="B7" s="28" t="n">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>R3  Лазерне сканування та BIM</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>400</v>
+      </c>
+      <c r="C7" s="23" t="n">
+        <v>560</v>
+      </c>
+      <c r="D7" s="23" t="n">
+        <v>784</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>1058</v>
+      </c>
+      <c r="F7" s="23" t="n">
+        <v>476</v>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" s="17" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J7" s="23">
+        <f>H7*I7</f>
+        <v/>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>НОВИЙ: CAGR 38% на регуляторному примусі (BIM у ДБН)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="inlineStr">
+        <is>
+          <t>R1  Топографія</t>
+        </is>
+      </c>
+      <c r="B8" s="28" t="n">
         <v>2860</v>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C8" s="28" t="n">
         <v>3089</v>
       </c>
-      <c r="D7" s="28" t="n">
+      <c r="D8" s="28" t="n">
         <v>3367</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E8" s="28" t="n">
         <v>3636</v>
       </c>
-      <c r="F7" s="28" t="n">
+      <c r="F8" s="28" t="n">
         <v>1236</v>
       </c>
-      <c r="G7" s="28" t="n">
+      <c r="G8" s="28" t="n">
         <v>20</v>
       </c>
-      <c r="H7" s="28" t="n">
-        <v>22</v>
-      </c>
-      <c r="I7" s="16" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="J7" s="28">
-        <f>H7*I7</f>
-        <v/>
-      </c>
-      <c r="K7" s="32" t="n">
-        <v>20</v>
-      </c>
-      <c r="L7" s="4" t="inlineStr">
-        <is>
-          <t>$6 796 на людину — найнижчий показник портфеля</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="31" t="inlineStr">
-        <is>
-          <t>M9  Надра й карʼєри: маркшейдерія + DaaS</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="n">
+      <c r="H8" s="28" t="n">
+        <v>16</v>
+      </c>
+      <c r="I8" s="16" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J8" s="28">
+        <f>H8*I8</f>
+        <v/>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>15</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>канал, не зростання: $5 452 на людину, конкуренція макс.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  R4 ізсередини — вертикалі:</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Мережі й комунальна інфраструктура</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>950</v>
+      </c>
+      <c r="C11" s="23" t="n">
+        <v>1159</v>
+      </c>
+      <c r="D11" s="23" t="n">
+        <v>1437</v>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>614</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="J11" s="23">
+        <f>H11*I11</f>
+        <v/>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>ядро R4: найвищий GM, найнижча конкуренція, LTV/CAC 8,5</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Дороги й інфраструктура</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="n">
+        <v>650</v>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>767</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>959</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>1189</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>357</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J12" s="10">
+        <f>H12*I12</f>
+        <v/>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>донорські інфрапроєкти, прозорість</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Надра й карʼєри</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="n">
         <v>380</v>
       </c>
-      <c r="C8" s="23" t="n">
+      <c r="C13" s="10" t="n">
         <v>426</v>
       </c>
-      <c r="D8" s="23" t="n">
+      <c r="D13" s="10" t="n">
         <v>481</v>
       </c>
-      <c r="E8" s="23" t="n">
+      <c r="E13" s="10" t="n">
         <v>534</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F13" s="10" t="n">
         <v>240</v>
       </c>
-      <c r="G8" s="23" t="n">
-        <v>5</v>
-      </c>
-      <c r="H8" s="23" t="n">
-        <v>22</v>
-      </c>
-      <c r="I8" s="17" t="n">
+      <c r="G13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="12" t="n">
         <v>0.66</v>
       </c>
-      <c r="J8" s="23">
-        <f>H8*I8</f>
-        <v/>
-      </c>
-      <c r="K8" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" s="4" t="inlineStr">
-        <is>
-          <t>обовʼязкові заміри, майже немає конкуренції</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>M3  ІТ-автоматизація для будівельників</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="n">
-        <v>990</v>
-      </c>
-      <c r="C9" s="10" t="n">
-        <v>1208</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>1510</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>1872</v>
-      </c>
-      <c r="F9" s="10" t="n">
-        <v>337</v>
-      </c>
-      <c r="G9" s="10" t="n">
-        <v>7</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <v>34</v>
-      </c>
-      <c r="I9" s="12" t="n">
+      <c r="J13" s="10">
+        <f>H13*I13</f>
+        <v/>
+      </c>
+      <c r="K13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>найвищий GM у R4, майже немає конкуренції</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Агро (GIS-ніша)</t>
+        </is>
+      </c>
+      <c r="B14" s="28" t="n">
+        <v>311</v>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>361</v>
+      </c>
+      <c r="D14" s="28" t="n">
+        <v>419</v>
+      </c>
+      <c r="E14" s="28" t="n">
+        <v>486</v>
+      </c>
+      <c r="F14" s="28" t="n">
+        <v>170</v>
+      </c>
+      <c r="G14" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="16" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J14" s="28">
+        <f>H14*I14</f>
+        <v/>
+      </c>
+      <c r="K14" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>НЕ ЙДЕМО: LTV/CAC 1,5, payback понад 30 міс</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Будівельники (ERP/BIM-процеси)</t>
+        </is>
+      </c>
+      <c r="B15" s="10" t="n">
+        <v>185</v>
+      </c>
+      <c r="C15" s="10" t="n">
+        <v>222</v>
+      </c>
+      <c r="D15" s="10" t="n">
+        <v>266</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>320</v>
+      </c>
+      <c r="F15" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="12" t="n">
         <v>0.45</v>
       </c>
-      <c r="J9" s="10">
-        <f>H9*I9</f>
-        <v/>
-      </c>
-      <c r="K9" s="11" t="n">
-        <v>9</v>
-      </c>
-      <c r="L9" s="4" t="inlineStr">
-        <is>
-          <t>BIM на держзамовленні, ЄДЕССБ; SAM лише 337 млн</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>M8  Розмінування: геодані + ІТ</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="n">
-        <v>260</v>
-      </c>
-      <c r="C10" s="10" t="n">
-        <v>299</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>353</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>406</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>162</v>
-      </c>
-      <c r="G10" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <v>13</v>
-      </c>
-      <c r="I10" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="J10" s="10">
-        <f>H10*I10</f>
-        <v/>
-      </c>
-      <c r="K10" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="L10" s="4" t="inlineStr">
-        <is>
-          <t>GIS = ядро IMSMA; фінансування політичне</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="29" t="inlineStr">
-        <is>
-          <t>M4  ІТ / цифра для агро</t>
-        </is>
-      </c>
-      <c r="B11" s="28" t="n">
-        <v>3890</v>
-      </c>
-      <c r="C11" s="28" t="n">
-        <v>4435</v>
-      </c>
-      <c r="D11" s="28" t="n">
-        <v>5055</v>
-      </c>
-      <c r="E11" s="28" t="n">
-        <v>5713</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>457</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="H11" s="28" t="n">
-        <v>27</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J11" s="28">
-        <f>H11*I11</f>
-        <v/>
-      </c>
-      <c r="K11" s="32" t="n">
-        <v>8</v>
-      </c>
-      <c r="L11" s="4" t="inlineStr">
-        <is>
-          <t>найбільший TAM — і LTV/CAC 1,8</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="31" t="inlineStr">
-        <is>
-          <t>M2  Інженерно-геологічні вишукування</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="n">
-        <v>2410</v>
-      </c>
-      <c r="C12" s="23" t="n">
-        <v>2579</v>
-      </c>
-      <c r="D12" s="23" t="n">
-        <v>2785</v>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>2980</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>894</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>27</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <v>82</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="J12" s="23">
-        <f>H12*I12</f>
-        <v/>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>29</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>ФАКТ 70 000 грн/день: GM 52%, обмежує капітал</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="29" t="inlineStr">
-        <is>
-          <t>M7  Громади / містобудівна документація</t>
-        </is>
-      </c>
-      <c r="B13" s="28" t="n">
+      <c r="J15" s="10">
+        <f>H15*I15</f>
+        <v/>
+      </c>
+      <c r="K15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>TAM ВИПРАВЛЕНО: було 990, знизу вгору 185</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Громади</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="n">
         <v>750</v>
       </c>
-      <c r="C13" s="28" t="n">
+      <c r="C16" s="28" t="n">
         <v>825</v>
       </c>
-      <c r="D13" s="28" t="n">
+      <c r="D16" s="28" t="n">
         <v>916</v>
       </c>
-      <c r="E13" s="28" t="n">
+      <c r="E16" s="28" t="n">
         <v>1007</v>
       </c>
-      <c r="F13" s="28" t="n">
+      <c r="F16" s="28" t="n">
         <v>252</v>
       </c>
-      <c r="G13" s="28" t="n">
-        <v>4</v>
-      </c>
-      <c r="H13" s="28" t="n">
-        <v>9</v>
-      </c>
-      <c r="I13" s="16" t="n">
+      <c r="G16" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="16" t="n">
         <v>0.4</v>
       </c>
-      <c r="J13" s="28">
-        <f>H13*I13</f>
-        <v/>
-      </c>
-      <c r="K13" s="32" t="n">
-        <v>3</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>тендери, демпінг, дрібні чеки</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="33" t="inlineStr">
-        <is>
-          <t>РАЗОМ</t>
-        </is>
-      </c>
-      <c r="B14" s="34">
-        <f>SUM(B5:B13)</f>
-        <v/>
-      </c>
-      <c r="C14" s="34">
-        <f>SUM(C5:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="34">
-        <f>SUM(D5:D13)</f>
-        <v/>
-      </c>
-      <c r="E14" s="34">
-        <f>SUM(E5:E13)</f>
-        <v/>
-      </c>
-      <c r="F14" s="34">
-        <f>SUM(F5:F13)</f>
-        <v/>
-      </c>
-      <c r="G14" s="34">
-        <f>SUM(G5:G13)</f>
-        <v/>
-      </c>
-      <c r="H14" s="34">
-        <f>SUM(H5:H13)</f>
-        <v/>
-      </c>
-      <c r="I14" s="33" t="n"/>
-      <c r="J14" s="34">
-        <f>SUM(J5:J13)</f>
-        <v/>
-      </c>
-      <c r="K14" s="35">
-        <f>SUM(K5:K13)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="36" t="inlineStr">
-        <is>
-          <t>Увесь внутрішній SOM потребує ~117 людей при плані 100. Геологія (M2) піднялась із останнього місця на друге за абсолютним валовим прибутком.</t>
+      <c r="J16" s="28">
+        <f>H16*I16</f>
+        <v/>
+      </c>
+      <c r="K16" s="32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>НЕ ЙДЕМО: демпінг, дрібні чеки, тендери</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="34" t="inlineStr">
+        <is>
+          <t>РАЗОМ чотири ринки</t>
+        </is>
+      </c>
+      <c r="B17" s="35">
+        <f>SUM(B5:B8)</f>
+        <v/>
+      </c>
+      <c r="C17" s="35">
+        <f>SUM(C5:C8)</f>
+        <v/>
+      </c>
+      <c r="D17" s="35">
+        <f>SUM(D5:D8)</f>
+        <v/>
+      </c>
+      <c r="E17" s="35">
+        <f>SUM(E5:E8)</f>
+        <v/>
+      </c>
+      <c r="F17" s="35">
+        <f>SUM(F5:F8)</f>
+        <v/>
+      </c>
+      <c r="G17" s="35">
+        <f>SUM(G5:G8)</f>
+        <v/>
+      </c>
+      <c r="H17" s="35">
+        <f>SUM(H5:H8)</f>
+        <v/>
+      </c>
+      <c r="I17" s="34" t="n"/>
+      <c r="J17" s="35">
+        <f>SUM(J5:J8)</f>
+        <v/>
+      </c>
+      <c r="K17" s="36">
+        <f>SUM(K5:K8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Лазерне сканування та BIM (R3) — найшвидший ринок із чотирьох (CAGR 38%), якого сьогодні в компанії немає взагалі: 0 → 40 млн грн.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="37" t="inlineStr">
+        <is>
+          <t>TAM для будівельників виправлено: зверху вниз давало 990 млн, знизу вгору — 185 млн. Завищення в 5,4 раза.</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2851,7 @@
       <c r="F6" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="37">
+      <c r="G6" s="38">
         <f>SUMPRODUCT(B6:F6,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -2822,7 +2887,7 @@
       <c r="F7" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="37">
+      <c r="G7" s="38">
         <f>SUMPRODUCT(B7:F7,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -2858,7 +2923,7 @@
       <c r="F8" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="37">
+      <c r="G8" s="38">
         <f>SUMPRODUCT(B8:F8,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -2894,7 +2959,7 @@
       <c r="F9" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G9" s="38">
+      <c r="G9" s="39">
         <f>SUMPRODUCT(B9:F9,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -2930,7 +2995,7 @@
       <c r="F10" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G10" s="38">
+      <c r="G10" s="39">
         <f>SUMPRODUCT(B10:F10,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -2966,7 +3031,7 @@
       <c r="F11" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="39">
         <f>SUMPRODUCT(B11:F11,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -3002,7 +3067,7 @@
       <c r="F12" s="32" t="n">
         <v>4</v>
       </c>
-      <c r="G12" s="39">
+      <c r="G12" s="40">
         <f>SUMPRODUCT(B12:F12,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -3038,7 +3103,7 @@
       <c r="F13" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="38">
         <f>SUMPRODUCT(B13:F13,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -3074,7 +3139,7 @@
       <c r="F14" s="32" t="n">
         <v>2</v>
       </c>
-      <c r="G14" s="39">
+      <c r="G14" s="40">
         <f>SUMPRODUCT(B14:F14,$B$5:$F$5)</f>
         <v/>
       </c>
@@ -3103,7 +3168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -3123,7 +3188,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="41" t="inlineStr">
         <is>
           <t>База 2026 — реконструкція за РИНКОВИМИ цінами і «легкою» структурою витрат, НЕ ваша звітність.</t>
         </is>
@@ -3182,13 +3247,13 @@
       <c r="B6" s="11" t="n">
         <v>12</v>
       </c>
-      <c r="C6" s="41" t="n">
+      <c r="C6" s="42" t="n">
         <v>26.9</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>0.44</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="42">
         <f>C6*D6</f>
         <v/>
       </c>
@@ -3211,13 +3276,13 @@
       <c r="B7" s="11" t="n">
         <v>22</v>
       </c>
-      <c r="C7" s="41" t="n">
+      <c r="C7" s="42" t="n">
         <v>19.6</v>
       </c>
       <c r="D7" s="12" t="n">
         <v>0.21</v>
       </c>
-      <c r="E7" s="41">
+      <c r="E7" s="42">
         <f>C7*D7</f>
         <v/>
       </c>
@@ -3240,13 +3305,13 @@
       <c r="B8" s="11" t="n">
         <v>10</v>
       </c>
-      <c r="C8" s="41" t="n">
+      <c r="C8" s="42" t="n">
         <v>17</v>
       </c>
       <c r="D8" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="E8" s="41">
+      <c r="E8" s="42">
         <f>C8*D8</f>
         <v/>
       </c>
@@ -3269,13 +3334,13 @@
       <c r="B9" s="11" t="n">
         <v>6</v>
       </c>
-      <c r="C9" s="41" t="n">
+      <c r="C9" s="42" t="n">
         <v>0</v>
       </c>
       <c r="D9" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="41">
+      <c r="E9" s="42">
         <f>C9*D9</f>
         <v/>
       </c>
@@ -3286,32 +3351,32 @@
       <c r="G9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="33" t="inlineStr">
+      <c r="A10" s="34" t="inlineStr">
         <is>
           <t>РАЗОМ</t>
         </is>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="34">
         <f>SUM(B6:B9)</f>
         <v/>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="43">
         <f>SUM(C6:C9)</f>
         <v/>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="44">
         <f>E10/C10</f>
         <v/>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="43">
         <f>SUM(E6:E9)</f>
         <v/>
       </c>
-      <c r="F10" s="34">
+      <c r="F10" s="35">
         <f>E10*1000000/45.0/B10</f>
         <v/>
       </c>
-      <c r="G10" s="33" t="inlineStr"/>
+      <c r="G10" s="34" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
@@ -3322,7 +3387,7 @@
       <c r="B11" s="9" t="n">
         <v>0.16</v>
       </c>
-      <c r="C11" s="44">
+      <c r="C11" s="45">
         <f>C10*B11</f>
         <v/>
       </c>
@@ -3333,21 +3398,21 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="33" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>EBITDA, млн грн</t>
         </is>
       </c>
-      <c r="B12" s="45" t="n"/>
-      <c r="C12" s="42">
+      <c r="B12" s="46" t="n"/>
+      <c r="C12" s="43">
         <f>E10-C11</f>
         <v/>
       </c>
-      <c r="D12" s="46">
+      <c r="D12" s="47">
         <f>C12/C10</f>
         <v/>
       </c>
-      <c r="E12" s="47">
+      <c r="E12" s="48">
         <f>C12*1000000/45.0</f>
         <v/>
       </c>
@@ -3360,7 +3425,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>ЦІЛЬ 2029 (~100 осіб) — тільки внутрішній ринок</t>
+          <t>ЦІЛЬ 2029 (~100 осіб) — чотири ринки</t>
         </is>
       </c>
     </row>
@@ -3404,19 +3469,19 @@
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>Геологія (8 бригад, util 70%)</t>
+          <t>R4 ІТ-розробка для індустрій (ядро — мережі)</t>
         </is>
       </c>
       <c r="B16" s="11" t="n">
-        <v>29</v>
-      </c>
-      <c r="C16" s="41" t="n">
-        <v>82.3</v>
+        <v>28</v>
+      </c>
+      <c r="C16" s="42" t="n">
+        <v>95.2</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="E16" s="41">
+        <v>0.58</v>
+      </c>
+      <c r="E16" s="42">
         <f>C16*D16</f>
         <v/>
       </c>
@@ -3426,26 +3491,26 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>СТАВКА 1: обмежує капітал ~$450 тис. на 5 УРБ</t>
+          <t>СТАВКА 1: двигун зростання, ROIC 957%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Мережі / комунальна інфра: продукт + підписка</t>
+          <t>R2 Інженерна геологія (7 бригад, util 70%)</t>
         </is>
       </c>
       <c r="B17" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="C17" s="41" t="n">
-        <v>65</v>
+        <v>26</v>
+      </c>
+      <c r="C17" s="42" t="n">
+        <v>74.40000000000001</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E17" s="41">
+        <v>0.52</v>
+      </c>
+      <c r="E17" s="42">
         <f>C17*D17</f>
         <v/>
       </c>
@@ -3455,26 +3520,26 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>СТАВКА 2: ~90 ентерпрайз-акаунтів</t>
+          <t>СТАВКА 3: грошова корова, фінансує R3 і R4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>Дороги / інфра: геодані і контроль</t>
+          <t>R3 Лазерне сканування та BIM</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C18" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C18" s="42" t="n">
         <v>40</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E18" s="41">
+        <v>0.55</v>
+      </c>
+      <c r="E18" s="42">
         <f>C18*D18</f>
         <v/>
       </c>
@@ -3484,26 +3549,26 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>СТАВКА 3: донорські інфрапроєкти</t>
+          <t>СТАВКА 2: новий напрямок, CAGR 38%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Надра / карʼєри: DaaS-заміри обсягів</t>
+          <t>R1 Топографія (канал продажів)</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C19" s="41" t="n">
-        <v>21</v>
+        <v>15</v>
+      </c>
+      <c r="C19" s="42" t="n">
+        <v>16.2</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="E19" s="41">
+        <v>0.26</v>
+      </c>
+      <c r="E19" s="42">
         <f>C19*D19</f>
         <v/>
       </c>
@@ -3513,26 +3578,26 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>СТАВКА 3: та сама технологія, що й дороги</t>
+          <t>не росте; дає доступ до 70 000 покупців</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Топогеодезія (8,3 бригади — канал продажів)</t>
+          <t>Адмін / продажі / маркетинг / R&amp;D</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="C20" s="41" t="n">
-        <v>21.6</v>
+        <v>11</v>
+      </c>
+      <c r="C20" s="42" t="n">
+        <v>0</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>0.336</v>
-      </c>
-      <c r="E20" s="41">
+        <v>0</v>
+      </c>
+      <c r="E20" s="42">
         <f>C20*D20</f>
         <v/>
       </c>
@@ -3540,166 +3605,137 @@
         <f>IF(B20=0,0,E20*1000000/51.5/B20)</f>
         <v/>
       </c>
-      <c r="G20" s="4" t="inlineStr">
-        <is>
-          <t>не росте; робить CAC підписки $1 800</t>
-        </is>
-      </c>
+      <c r="G20" s="4" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>Адмін / продажі / маркетинг / R&amp;D</t>
-        </is>
-      </c>
-      <c r="B21" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="C21" s="41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="41">
-        <f>C21*D21</f>
-        <v/>
-      </c>
-      <c r="F21" s="10">
-        <f>IF(B21=0,0,E21*1000000/51.5/B21)</f>
-        <v/>
-      </c>
-      <c r="G21" s="4" t="inlineStr"/>
+      <c r="A21" s="34" t="inlineStr">
+        <is>
+          <t>РАЗОМ</t>
+        </is>
+      </c>
+      <c r="B21" s="34">
+        <f>SUM(B16:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="43">
+        <f>SUM(C16:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="44">
+        <f>E21/C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="43">
+        <f>SUM(E16:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="35">
+        <f>E21*1000000/51.5/B21</f>
+        <v/>
+      </c>
+      <c r="G21" s="34" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="33" t="inlineStr">
-        <is>
-          <t>РАЗОМ</t>
-        </is>
-      </c>
-      <c r="B22" s="33">
-        <f>SUM(B16:B21)</f>
-        <v/>
-      </c>
-      <c r="C22" s="42">
-        <f>SUM(C16:C21)</f>
-        <v/>
-      </c>
-      <c r="D22" s="43">
-        <f>E22/C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="42">
-        <f>SUM(E16:E21)</f>
-        <v/>
-      </c>
-      <c r="F22" s="34">
-        <f>E22*1000000/51.5/B22</f>
-        <v/>
-      </c>
-      <c r="G22" s="33" t="inlineStr"/>
+      <c r="A22" s="18" t="inlineStr">
+        <is>
+          <t>SG&amp;A, % від виручки</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="C22" s="45">
+        <f>C21*B22</f>
+        <v/>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>вище, бо зʼявляються продажі й маркетинг продукту</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
-        <is>
-          <t>SG&amp;A, % від виручки</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="C23" s="44">
-        <f>C22*B23</f>
-        <v/>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>вище, бо зʼявляються продажі й маркетинг продукту</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="33" t="inlineStr">
+      <c r="A23" s="34" t="inlineStr">
         <is>
           <t>EBITDA, млн грн</t>
         </is>
       </c>
-      <c r="B24" s="45" t="n"/>
-      <c r="C24" s="42">
-        <f>E22-C23</f>
-        <v/>
-      </c>
-      <c r="D24" s="46">
-        <f>C24/C22</f>
-        <v/>
-      </c>
-      <c r="E24" s="47">
-        <f>C24*1000000/51.5</f>
-        <v/>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="B23" s="46" t="n"/>
+      <c r="C23" s="43">
+        <f>E21-C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="47">
+        <f>C23/C21</f>
+        <v/>
+      </c>
+      <c r="E23" s="48">
+        <f>C23*1000000/51.5</f>
+        <v/>
+      </c>
+      <c r="F23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="49" t="inlineStr">
+        <is>
+          <t>ДЕЛЬТА 2026 → 2029</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="48" t="inlineStr">
-        <is>
-          <t>ДЕЛЬТА 2026 → 2029</t>
-        </is>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Виручка</t>
+        </is>
+      </c>
+      <c r="B26" s="50">
+        <f>C21/C10</f>
+        <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Виручка</t>
-        </is>
-      </c>
-      <c r="B27" s="49">
-        <f>C22/C10</f>
+          <t>Валовий прибуток</t>
+        </is>
+      </c>
+      <c r="B27" s="50">
+        <f>E21/E10</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Валовий прибуток</t>
-        </is>
-      </c>
-      <c r="B28" s="49">
-        <f>E22/E10</f>
+          <t>Валовий прибуток на 1 FTE</t>
+        </is>
+      </c>
+      <c r="B28" s="50">
+        <f>F21/F10</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Валовий прибуток на 1 FTE</t>
-        </is>
-      </c>
-      <c r="B29" s="49">
-        <f>F22/F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
           <t>EBITDA, млн грн</t>
         </is>
       </c>
-      <c r="B30" s="44">
+      <c r="B29" s="45">
         <f>C12</f>
         <v/>
       </c>
-      <c r="C30" s="50" t="inlineStr">
+      <c r="C29" s="51" t="inlineStr">
         <is>
           <t>→</t>
         </is>
       </c>
-      <c r="D30" s="51">
-        <f>C24</f>
+      <c r="D29" s="52">
+        <f>C23</f>
         <v/>
       </c>
     </row>
@@ -3738,7 +3774,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="40" t="inlineStr">
+      <c r="A2" s="41" t="inlineStr">
         <is>
           <t>Без експорту всі шість напрямків живляться з одного джерела: бюджету й донорських грошей.</t>
         </is>
@@ -3785,15 +3821,15 @@
       <c r="B5" s="9" t="n">
         <v>0.55</v>
       </c>
-      <c r="C5" s="52" t="n">
+      <c r="C5" s="53" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="10">
-        <f>(82.3+65+40+21+21.6)*C5</f>
+        <f>(95.2+74.4+40+16.2)*C5</f>
         <v/>
       </c>
       <c r="E5" s="10">
-        <f>(82.3*0.518+65*0.62+40*0.52+21*0.66+21.6*0.336)*C5-D5*0.27</f>
+        <f>(95.2*0.58+74.4*0.52+40*0.55+16.2*0.26)*C5-D5*0.27</f>
         <v/>
       </c>
       <c r="F5" s="4" t="inlineStr">
@@ -3811,15 +3847,15 @@
       <c r="B6" s="9" t="n">
         <v>0.25</v>
       </c>
-      <c r="C6" s="52" t="n">
+      <c r="C6" s="53" t="n">
         <v>1.85</v>
       </c>
       <c r="D6" s="10">
-        <f>(82.3+65+40+21+21.6)*C6</f>
+        <f>(95.2+74.4+40+16.2)*C6</f>
         <v/>
       </c>
       <c r="E6" s="10">
-        <f>(82.3*0.518+65*0.62+40*0.52+21*0.66+21.6*0.336)*C6-D6*0.27</f>
+        <f>(95.2*0.58+74.4*0.52+40*0.55+16.2*0.26)*C6-D6*0.27</f>
         <v/>
       </c>
       <c r="F6" s="4" t="inlineStr">
@@ -3837,15 +3873,15 @@
       <c r="B7" s="16" t="n">
         <v>0.2</v>
       </c>
-      <c r="C7" s="53" t="n">
+      <c r="C7" s="54" t="n">
         <v>0.5</v>
       </c>
       <c r="D7" s="28">
-        <f>(82.3+65+40+21+21.6)*C7</f>
+        <f>(95.2+74.4+40+16.2)*C7</f>
         <v/>
       </c>
       <c r="E7" s="28">
-        <f>(82.3*0.518+65*0.62+40*0.52+21*0.66+21.6*0.336)*C7-D7*0.27</f>
+        <f>(95.2*0.58+74.4*0.52+40*0.55+16.2*0.26)*C7-D7*0.27</f>
         <v/>
       </c>
       <c r="F7" s="29" t="inlineStr">
@@ -3855,24 +3891,24 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="33" t="inlineStr">
+      <c r="A8" s="34" t="inlineStr">
         <is>
           <t>ОЧІКУВАНЕ ЗНАЧЕННЯ (зважене)</t>
         </is>
       </c>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="34">
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="35">
         <f>SUMPRODUCT(B5:B7,D5:D7)</f>
         <v/>
       </c>
-      <c r="E8" s="34">
+      <c r="E8" s="35">
         <f>SUMPRODUCT(B5:B7,E5:E7)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="36" t="inlineStr">
+      <c r="A10" s="37" t="inlineStr">
         <is>
           <t>Раніше експорт тримав нижню межу: внутрішні ринки падали на 45%, валютна лінія майже ні. Тепер такої лінії немає.</t>
         </is>
@@ -3884,4 +3920,625 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ЮНІТ-ЕКОНОМІКА ЧОТИРЬОХ РИНКІВ — ПОКУПЕЦЬ ЯК ЮНІТ</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Жовті комірки редагуються. LTV, LTV/CAC, payback, ROIC і бал рахуються формулами. Курс 51,5 грн/$.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Ринок</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Юніт</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Чек, грн</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>Повторів/рік</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Років життя</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>GM</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>CAC, грн</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Виручка/FTE, млн</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>CapEx/FTE $</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Конкур. 1-5</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>SAM 2029</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>R1 Топографія</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>обʼєкт / замовлення</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H5" s="53" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="I5" s="8" t="n">
+        <v>9600</v>
+      </c>
+      <c r="J5" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>R2 Інженерна геологія</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>обʼєкт / замовлення</t>
+        </is>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>250000</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>12000</v>
+      </c>
+      <c r="H6" s="53" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="I6" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>R3 Лазерне сканування та BIM</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>обʼєкт / проєкт</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>400000</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H7" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="8" t="n">
+        <v>9500</v>
+      </c>
+      <c r="J7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>R4 ІТ-розробка для індустрій</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>клієнт / підписка</t>
+        </is>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>721000</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>300000</v>
+      </c>
+      <c r="H8" s="53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I8" s="8" t="n">
+        <v>4000</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>1392</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>РОЗРАХУНОК</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Ринок</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>LTV $</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>CAC $</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>LTV / CAC</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Payback, міс</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>ВП/FTE $</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>ROIC</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>ВП на SAM, млн</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr"/>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4">
+        <f>A5</f>
+        <v/>
+      </c>
+      <c r="B12" s="23">
+        <f>C5*D5*E5*F5/51.5</f>
+        <v/>
+      </c>
+      <c r="C12" s="23">
+        <f>G5/51.5</f>
+        <v/>
+      </c>
+      <c r="D12" s="55">
+        <f>B12/C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="55">
+        <f>C12/(C5*D5*F5/12/51.5)</f>
+        <v/>
+      </c>
+      <c r="F12" s="15">
+        <f>H5*F5*1000000/51.5</f>
+        <v/>
+      </c>
+      <c r="G12" s="17">
+        <f>F12/I5</f>
+        <v/>
+      </c>
+      <c r="H12" s="23">
+        <f>K5*F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4">
+        <f>A6</f>
+        <v/>
+      </c>
+      <c r="B13" s="23">
+        <f>C6*D6*E6*F6/51.5</f>
+        <v/>
+      </c>
+      <c r="C13" s="23">
+        <f>G6/51.5</f>
+        <v/>
+      </c>
+      <c r="D13" s="55">
+        <f>B13/C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="55">
+        <f>C13/(C6*D6*F6/12/51.5)</f>
+        <v/>
+      </c>
+      <c r="F13" s="15">
+        <f>H6*F6*1000000/51.5</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>F13/I6</f>
+        <v/>
+      </c>
+      <c r="H13" s="23">
+        <f>K6*F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4">
+        <f>A7</f>
+        <v/>
+      </c>
+      <c r="B14" s="23">
+        <f>C7*D7*E7*F7/51.5</f>
+        <v/>
+      </c>
+      <c r="C14" s="23">
+        <f>G7/51.5</f>
+        <v/>
+      </c>
+      <c r="D14" s="55">
+        <f>B14/C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="55">
+        <f>C14/(C7*D7*F7/12/51.5)</f>
+        <v/>
+      </c>
+      <c r="F14" s="15">
+        <f>H7*F7*1000000/51.5</f>
+        <v/>
+      </c>
+      <c r="G14" s="17">
+        <f>F14/I7</f>
+        <v/>
+      </c>
+      <c r="H14" s="23">
+        <f>K7*F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4">
+        <f>A8</f>
+        <v/>
+      </c>
+      <c r="B15" s="23">
+        <f>C8*D8*E8*F8/51.5</f>
+        <v/>
+      </c>
+      <c r="C15" s="23">
+        <f>G8/51.5</f>
+        <v/>
+      </c>
+      <c r="D15" s="55">
+        <f>B15/C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="55">
+        <f>C15/(C8*D8*F8/12/51.5)</f>
+        <v/>
+      </c>
+      <c r="F15" s="15">
+        <f>H8*F8*1000000/51.5</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f>F15/I8</f>
+        <v/>
+      </c>
+      <c r="H15" s="23">
+        <f>K8*F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Поріг інвестора: LTV/CAC &gt; 3 і payback &lt; 12 міс. Усі чотири ринки проходять.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ПЕРЕВІРКА ОБСЯГУ РИНКУ: ДВІ НЕЗАЛЕЖНІ ОЦІНКИ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>Ринок</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Зверху вниз</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Покупців</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>× річний чек</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>Знизу вгору</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Розбіжність</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Вердикт</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>R1 Топографія</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>2860</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>70000</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>40000</v>
+      </c>
+      <c r="E20" s="10">
+        <f>C20*D20/1000000</f>
+        <v/>
+      </c>
+      <c r="F20" s="12">
+        <f>E20/B20-1</f>
+        <v/>
+      </c>
+      <c r="G20" s="4">
+        <f>IF(ABS(F20)&lt;0.35,"✓ підтверджено","⚠ ЦИФРІ НЕ ДОВІРЯТИ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>R2 Інженерна геологія</t>
+        </is>
+      </c>
+      <c r="B21" s="10" t="n">
+        <v>2410</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E21" s="10">
+        <f>C21*D21/1000000</f>
+        <v/>
+      </c>
+      <c r="F21" s="12">
+        <f>E21/B21-1</f>
+        <v/>
+      </c>
+      <c r="G21" s="4">
+        <f>IF(ABS(F21)&lt;0.35,"✓ підтверджено","⚠ ЦИФРІ НЕ ДОВІРЯТИ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>R3 Лазерне сканування та BIM</t>
+        </is>
+      </c>
+      <c r="B22" s="10" t="n">
+        <v>428</v>
+      </c>
+      <c r="C22" s="10" t="n">
+        <v>1030</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E22" s="10">
+        <f>C22*D22/1000000</f>
+        <v/>
+      </c>
+      <c r="F22" s="12">
+        <f>E22/B22-1</f>
+        <v/>
+      </c>
+      <c r="G22" s="4">
+        <f>IF(ABS(F22)&lt;0.35,"✓ підтверджено","⚠ ЦИФРІ НЕ ДОВІРЯТИ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="29" t="inlineStr">
+        <is>
+          <t>R4.5 Будівельники (в складі R4)</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="n">
+        <v>990</v>
+      </c>
+      <c r="C23" s="28" t="n">
+        <v>410</v>
+      </c>
+      <c r="D23" s="28" t="n">
+        <v>450000</v>
+      </c>
+      <c r="E23" s="28">
+        <f>C23*D23/1000000</f>
+        <v/>
+      </c>
+      <c r="F23" s="16">
+        <f>E23/B23-1</f>
+        <v/>
+      </c>
+      <c r="G23" s="29">
+        <f>IF(ABS(F23)&lt;0.35,"✓ підтверджено","⚠ ЦИФРІ НЕ ДОВІРЯТИ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Розбіжність до ±35% — норма. Більше — оцінка зроблена лише одним методом і не перевірена.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A18:K18"/>
+    <mergeCell ref="A10:K10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/market-analysis/unit-economics-model.xlsx
+++ b/market-analysis/unit-economics-model.xlsx
@@ -3776,7 +3776,7 @@
     <row r="2">
       <c r="A2" s="41" t="inlineStr">
         <is>
-          <t>Без експорту всі шість напрямків живляться з одного джерела: бюджету й донорських грошей.</t>
+          <t>Без експорту всі чотири ринки живляться з одного джерела: бюджету й донорських грошей.</t>
         </is>
       </c>
     </row>
@@ -4081,7 +4081,7 @@
         <v>12000</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>2.86</v>
+        <v>2.8615</v>
       </c>
       <c r="I6" s="8" t="n">
         <v>25000</v>

--- a/market-analysis/unit-economics-model.xlsx
+++ b/market-analysis/unit-economics-model.xlsx
@@ -3928,7 +3928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3947,7 +3947,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ЮНІТ-ЕКОНОМІКА ЧОТИРЬОХ РИНКІВ — ПОКУПЕЦЬ ЯК ЮНІТ</t>
+          <t>ЮНІТ-ЕКОНОМІКА РИНКІВ — ПОКУПЕЦЬ ЯК ЮНІТ</t>
         </is>
       </c>
     </row>
@@ -4171,103 +4171,108 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>R5 Розумна територія (суміжний)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>клієнт-майданчик</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>480000</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>180000</v>
+      </c>
+      <c r="H9" s="53" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>6000</v>
+      </c>
+      <c r="J9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>РОЗРАХУНОК</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>Ринок</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>LTV $</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>CAC $</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>LTV / CAC</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>Payback, міс</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>ВП/FTE $</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H12" s="3" t="inlineStr">
         <is>
           <t>ВП на SAM, млн</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr"/>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="4">
-        <f>A5</f>
-        <v/>
-      </c>
-      <c r="B12" s="23">
-        <f>C5*D5*E5*F5/51.5</f>
-        <v/>
-      </c>
-      <c r="C12" s="23">
-        <f>G5/51.5</f>
-        <v/>
-      </c>
-      <c r="D12" s="55">
-        <f>B12/C12</f>
-        <v/>
-      </c>
-      <c r="E12" s="55">
-        <f>C12/(C5*D5*F5/12/51.5)</f>
-        <v/>
-      </c>
-      <c r="F12" s="15">
-        <f>H5*F5*1000000/51.5</f>
-        <v/>
-      </c>
-      <c r="G12" s="17">
-        <f>F12/I5</f>
-        <v/>
-      </c>
-      <c r="H12" s="23">
-        <f>K5*F5</f>
-        <v/>
-      </c>
+      <c r="I12" s="3" t="inlineStr"/>
+      <c r="J12" s="3" t="inlineStr"/>
+      <c r="K12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4">
-        <f>A6</f>
+        <f>A5</f>
         <v/>
       </c>
       <c r="B13" s="23">
-        <f>C6*D6*E6*F6/51.5</f>
+        <f>C5*D5*E5*F5/51.5</f>
         <v/>
       </c>
       <c r="C13" s="23">
-        <f>G6/51.5</f>
+        <f>G5/51.5</f>
         <v/>
       </c>
       <c r="D13" s="55">
@@ -4275,33 +4280,33 @@
         <v/>
       </c>
       <c r="E13" s="55">
-        <f>C13/(C6*D6*F6/12/51.5)</f>
+        <f>C13/(C5*D5*F5/12/51.5)</f>
         <v/>
       </c>
       <c r="F13" s="15">
-        <f>H6*F6*1000000/51.5</f>
+        <f>H5*F5*1000000/51.5</f>
         <v/>
       </c>
       <c r="G13" s="17">
-        <f>F13/I6</f>
+        <f>F13/I5</f>
         <v/>
       </c>
       <c r="H13" s="23">
-        <f>K6*F6</f>
+        <f>K5*F5</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4">
-        <f>A7</f>
+        <f>A6</f>
         <v/>
       </c>
       <c r="B14" s="23">
-        <f>C7*D7*E7*F7/51.5</f>
+        <f>C6*D6*E6*F6/51.5</f>
         <v/>
       </c>
       <c r="C14" s="23">
-        <f>G7/51.5</f>
+        <f>G6/51.5</f>
         <v/>
       </c>
       <c r="D14" s="55">
@@ -4309,33 +4314,33 @@
         <v/>
       </c>
       <c r="E14" s="55">
-        <f>C14/(C7*D7*F7/12/51.5)</f>
+        <f>C14/(C6*D6*F6/12/51.5)</f>
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>H7*F7*1000000/51.5</f>
+        <f>H6*F6*1000000/51.5</f>
         <v/>
       </c>
       <c r="G14" s="17">
-        <f>F14/I7</f>
+        <f>F14/I6</f>
         <v/>
       </c>
       <c r="H14" s="23">
-        <f>K7*F7</f>
+        <f>K6*F6</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4">
-        <f>A8</f>
+        <f>A7</f>
         <v/>
       </c>
       <c r="B15" s="23">
-        <f>C8*D8*E8*F8/51.5</f>
+        <f>C7*D7*E7*F7/51.5</f>
         <v/>
       </c>
       <c r="C15" s="23">
-        <f>G8/51.5</f>
+        <f>G7/51.5</f>
         <v/>
       </c>
       <c r="D15" s="55">
@@ -4343,147 +4348,159 @@
         <v/>
       </c>
       <c r="E15" s="55">
-        <f>C15/(C8*D8*F8/12/51.5)</f>
+        <f>C15/(C7*D7*F7/12/51.5)</f>
         <v/>
       </c>
       <c r="F15" s="15">
+        <f>H7*F7*1000000/51.5</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f>F15/I7</f>
+        <v/>
+      </c>
+      <c r="H15" s="23">
+        <f>K7*F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4">
+        <f>A8</f>
+        <v/>
+      </c>
+      <c r="B16" s="23">
+        <f>C8*D8*E8*F8/51.5</f>
+        <v/>
+      </c>
+      <c r="C16" s="23">
+        <f>G8/51.5</f>
+        <v/>
+      </c>
+      <c r="D16" s="55">
+        <f>B16/C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="55">
+        <f>C16/(C8*D8*F8/12/51.5)</f>
+        <v/>
+      </c>
+      <c r="F16" s="15">
         <f>H8*F8*1000000/51.5</f>
         <v/>
       </c>
-      <c r="G15" s="17">
-        <f>F15/I8</f>
-        <v/>
-      </c>
-      <c r="H15" s="23">
+      <c r="G16" s="17">
+        <f>F16/I8</f>
+        <v/>
+      </c>
+      <c r="H16" s="23">
         <f>K8*F8</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="22" t="inlineStr">
-        <is>
-          <t>Поріг інвестора: LTV/CAC &gt; 3 і payback &lt; 12 міс. Усі чотири ринки проходять.</t>
-        </is>
+    <row r="17">
+      <c r="A17" s="4">
+        <f>A9</f>
+        <v/>
+      </c>
+      <c r="B17" s="23">
+        <f>C9*D9*E9*F9/51.5</f>
+        <v/>
+      </c>
+      <c r="C17" s="23">
+        <f>G9/51.5</f>
+        <v/>
+      </c>
+      <c r="D17" s="55">
+        <f>B17/C17</f>
+        <v/>
+      </c>
+      <c r="E17" s="55">
+        <f>C17/(C9*D9*F9/12/51.5)</f>
+        <v/>
+      </c>
+      <c r="F17" s="15">
+        <f>H9*F9*1000000/51.5</f>
+        <v/>
+      </c>
+      <c r="G17" s="17">
+        <f>F17/I9</f>
+        <v/>
+      </c>
+      <c r="H17" s="23">
+        <f>K9*F9</f>
+        <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Поріг інвестора: LTV/CAC &gt; 3 і payback &lt; 12 міс. Проходять усі, включно з R5. Для клієнта, якому вже робили сканування, CAC R5 падає до 60 тис. грн: LTV/CAC 22,8, payback 2,6 міс.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>ПЕРЕВІРКА ОБСЯГУ РИНКУ: ДВІ НЕЗАЛЕЖНІ ОЦІНКИ</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Ринок</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Зверху вниз</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Покупців</t>
         </is>
       </c>
-      <c r="D19" s="3" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>× річний чек</t>
         </is>
       </c>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>Знизу вгору</t>
         </is>
       </c>
-      <c r="F19" s="3" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>Розбіжність</t>
         </is>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Вердикт</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr"/>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>R1 Топографія</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>2860</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <v>70000</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>40000</v>
-      </c>
-      <c r="E20" s="10">
-        <f>C20*D20/1000000</f>
-        <v/>
-      </c>
-      <c r="F20" s="12">
-        <f>E20/B20-1</f>
-        <v/>
-      </c>
-      <c r="G20" s="4">
-        <f>IF(ABS(F20)&lt;0.35,"✓ підтверджено","⚠ ЦИФРІ НЕ ДОВІРЯТИ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>R2 Інженерна геологія</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="n">
-        <v>2410</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <v>12000</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>200000</v>
-      </c>
-      <c r="E21" s="10">
-        <f>C21*D21/1000000</f>
-        <v/>
-      </c>
-      <c r="F21" s="12">
-        <f>E21/B21-1</f>
-        <v/>
-      </c>
-      <c r="G21" s="4">
-        <f>IF(ABS(F21)&lt;0.35,"✓ підтверджено","⚠ ЦИФРІ НЕ ДОВІРЯТИ")</f>
-        <v/>
-      </c>
+      <c r="H21" s="3" t="inlineStr"/>
+      <c r="I21" s="3" t="inlineStr"/>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>R3 Лазерне сканування та BIM</t>
+          <t>R1 Топографія</t>
         </is>
       </c>
       <c r="B22" s="10" t="n">
-        <v>428</v>
+        <v>2860</v>
       </c>
       <c r="C22" s="10" t="n">
-        <v>1030</v>
+        <v>70000</v>
       </c>
       <c r="D22" s="10" t="n">
-        <v>350000</v>
+        <v>40000</v>
       </c>
       <c r="E22" s="10">
         <f>C22*D22/1000000</f>
@@ -4499,35 +4516,119 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>R2 Інженерна геологія</t>
+        </is>
+      </c>
+      <c r="B23" s="10" t="n">
+        <v>2410</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>200000</v>
+      </c>
+      <c r="E23" s="10">
+        <f>C23*D23/1000000</f>
+        <v/>
+      </c>
+      <c r="F23" s="12">
+        <f>E23/B23-1</f>
+        <v/>
+      </c>
+      <c r="G23" s="4">
+        <f>IF(ABS(F23)&lt;0.35,"✓ підтверджено","⚠ ЦИФРІ НЕ ДОВІРЯТИ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>R3 Лазерне сканування та BIM</t>
+        </is>
+      </c>
+      <c r="B24" s="10" t="n">
+        <v>428</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <v>1030</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>350000</v>
+      </c>
+      <c r="E24" s="10">
+        <f>C24*D24/1000000</f>
+        <v/>
+      </c>
+      <c r="F24" s="12">
+        <f>E24/B24-1</f>
+        <v/>
+      </c>
+      <c r="G24" s="4">
+        <f>IF(ABS(F24)&lt;0.35,"✓ підтверджено","⚠ ЦИФРІ НЕ ДОВІРЯТИ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="29" t="inlineStr">
         <is>
           <t>R4.5 Будівельники (в складі R4)</t>
         </is>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B25" s="28" t="n">
         <v>990</v>
       </c>
-      <c r="C23" s="28" t="n">
+      <c r="C25" s="28" t="n">
         <v>410</v>
       </c>
-      <c r="D23" s="28" t="n">
+      <c r="D25" s="28" t="n">
         <v>450000</v>
       </c>
-      <c r="E23" s="28">
-        <f>C23*D23/1000000</f>
-        <v/>
-      </c>
-      <c r="F23" s="16">
-        <f>E23/B23-1</f>
-        <v/>
-      </c>
-      <c r="G23" s="29">
-        <f>IF(ABS(F23)&lt;0.35,"✓ підтверджено","⚠ ЦИФРІ НЕ ДОВІРЯТИ")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="E25" s="28">
+        <f>C25*D25/1000000</f>
+        <v/>
+      </c>
+      <c r="F25" s="16">
+        <f>E25/B25-1</f>
+        <v/>
+      </c>
+      <c r="G25" s="29">
+        <f>IF(ABS(F25)&lt;0.35,"✓ підтверджено","⚠ ЦИФРІ НЕ ДОВІРЯТИ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>R5 Розумна територія</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="n">
+        <v>240</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <v>194</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <v>1056000</v>
+      </c>
+      <c r="E26" s="10">
+        <f>C26*D26/1000000</f>
+        <v/>
+      </c>
+      <c r="F26" s="12">
+        <f>E26/B26-1</f>
+        <v/>
+      </c>
+      <c r="G26" s="4">
+        <f>IF(ABS(F26)&lt;0.35,"✓ підтверджено","⚠ ЦИФРІ НЕ ДОВІРЯТИ")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>Розбіжність до ±35% — норма. Більше — оцінка зроблена лише одним методом і не перевірена.</t>
         </is>
@@ -4535,9 +4636,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
+    <mergeCell ref="A11:K11"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A20:K20"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
